--- a/correlations/HI_tauc/HI_tauc_correlations_V2_predefense.xlsx
+++ b/correlations/HI_tauc/HI_tauc_correlations_V2_predefense.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\correlations\HI_tauc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70A7212D-5D86-4FA6-A9C1-9B8274B0EFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529151E7-A44D-4E04-9DB0-4BD2B792916E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
+    <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
   </bookViews>
   <sheets>
     <sheet name="with st7" sheetId="1" r:id="rId1"/>
     <sheet name="no st7" sheetId="3" r:id="rId2"/>
+    <sheet name="turb vs SS HI" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="83">
   <si>
     <t>Storm</t>
   </si>
@@ -502,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -626,10 +627,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -641,15 +642,14 @@
     <xf numFmtId="166" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -658,25 +658,13 @@
     <xf numFmtId="166" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -24328,6 +24316,826 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Spring</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="8.5024278215223098E-2"/>
+                  <c:y val="-0.13557633420822396"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$B$8:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>9.4513218106104094E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.2663094228711902E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.8732929175135894E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.9463558010346702E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.10415722716452799</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.66251429291673E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.0894558490112708E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.7278096303121701E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.0373962034653699E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.50118292734785E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$C$8:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>5.1856335362832198E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.103368750113241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.15621819275209001</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.15071577677020101</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.5397551503622099E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6.9883057908481996E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.8645648239850305E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.12</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.101236914763633</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.107400232693555</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8DD7-4489-96F6-9F19D9716714}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1299336592"/>
+        <c:axId val="1113722480"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1299336592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1113722480"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1113722480"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1299336592"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Summer</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.12952209098862641"/>
+                  <c:y val="-3.7116870807815693E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.57681691180727601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13233171245622599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9326261366187695E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.14884070399999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.164262280281398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.45444212598241E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B59C-477A-96C7-97827DE0BAEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1351180048"/>
+        <c:axId val="1113714800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1351180048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1113714800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1113714800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1351180048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -30887,6 +31695,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors33.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors34.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -44028,6 +44916,1038 @@
 </file>
 
 <file path=xl/charts/style32.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style33.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style34.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -48863,6 +50783,83 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{609D4148-200F-AFE3-F125-B8F3B18F0B0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>157162</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>461962</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47EE037C-C8A8-F31B-4620-C3A1C958B496}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -49880,7 +51877,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E16" s="18">
-        <f>D16/C16</f>
+        <f t="shared" ref="E16:E21" si="1">D16/C16</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F16" s="18">
@@ -49914,7 +51911,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E17" s="18">
-        <f>D17/C17</f>
+        <f t="shared" si="1"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F17" s="18">
@@ -49948,7 +51945,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E18" s="18">
-        <f>D18/C18</f>
+        <f t="shared" si="1"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F18" s="18">
@@ -49982,7 +51979,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E19" s="18">
-        <f>D19/C19</f>
+        <f t="shared" si="1"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F19" s="18">
@@ -50016,7 +52013,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E20" s="18">
-        <f>D20/C20</f>
+        <f t="shared" si="1"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F20" s="18">
@@ -50072,7 +52069,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E21" s="18">
-        <f>D21/C21</f>
+        <f t="shared" si="1"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F21" s="18">
@@ -50328,7 +52325,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" ref="I26:I28" si="1">G26-H26</f>
+        <f t="shared" ref="I26:I28" si="2">G26-H26</f>
         <v>0.25</v>
       </c>
       <c r="J26" s="1"/>
@@ -50388,7 +52385,7 @@
         <v>3.5</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>-3.25</v>
       </c>
       <c r="J27" s="1"/>
@@ -50440,7 +52437,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J28" s="1"/>
@@ -50619,7 +52616,7 @@
         <v>0.5</v>
       </c>
       <c r="I31" s="15">
-        <f t="shared" ref="I31" si="2">G31-H31</f>
+        <f t="shared" ref="I31" si="3">G31-H31</f>
         <v>-0.5</v>
       </c>
       <c r="J31" s="1"/>
@@ -50778,7 +52775,7 @@
         <v>1.25</v>
       </c>
       <c r="I34" s="15">
-        <f t="shared" ref="I34" si="3">G34-H34</f>
+        <f t="shared" ref="I34" si="4">G34-H34</f>
         <v>-0.75</v>
       </c>
       <c r="J34" s="1"/>
@@ -50889,7 +52886,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E36" s="18">
-        <f>D36/C36</f>
+        <f t="shared" ref="E36:E41" si="5">D36/C36</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F36" s="18">
@@ -50902,7 +52899,7 @@
         <v>1.5</v>
       </c>
       <c r="I36" s="15">
-        <f t="shared" ref="I36:I41" si="4">G36-H36</f>
+        <f t="shared" ref="I36:I41" si="6">G36-H36</f>
         <v>-1</v>
       </c>
       <c r="J36" s="1"/>
@@ -50978,7 +52975,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E37" s="18">
-        <f>D37/C37</f>
+        <f t="shared" si="5"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F37" s="18">
@@ -50991,7 +52988,7 @@
         <v>1.25</v>
       </c>
       <c r="I37" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-1.25</v>
       </c>
       <c r="J37" s="1"/>
@@ -51067,7 +53064,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E38" s="18">
-        <f>D38/C38</f>
+        <f t="shared" si="5"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F38" s="18">
@@ -51080,7 +53077,7 @@
         <v>4.75</v>
       </c>
       <c r="I38" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-3.5</v>
       </c>
       <c r="J38" s="1"/>
@@ -51156,7 +53153,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E39" s="18">
-        <f>D39/C39</f>
+        <f t="shared" si="5"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F39" s="18">
@@ -51169,7 +53166,7 @@
         <v>2</v>
       </c>
       <c r="I39" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-0.75</v>
       </c>
       <c r="J39" s="1"/>
@@ -51191,7 +53188,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E40" s="18">
-        <f>D40/C40</f>
+        <f t="shared" si="5"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F40" s="18">
@@ -51204,7 +53201,7 @@
         <v>7.25</v>
       </c>
       <c r="I40" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-3.5</v>
       </c>
       <c r="J40" s="1"/>
@@ -51246,7 +53243,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E41" s="18">
-        <f>D41/C41</f>
+        <f t="shared" si="5"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F41" s="18">
@@ -51259,7 +53256,7 @@
         <v>4.75</v>
       </c>
       <c r="I41" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>-4.25</v>
       </c>
       <c r="J41" s="1"/>
@@ -51453,7 +53450,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="15">
-        <f t="shared" ref="I45:I47" si="5">G45-H45</f>
+        <f t="shared" ref="I45:I47" si="7">G45-H45</f>
         <v>0.25</v>
       </c>
       <c r="J45" s="1"/>
@@ -51513,7 +53510,7 @@
         <v>3.5</v>
       </c>
       <c r="I46" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-3.25</v>
       </c>
       <c r="J46" s="1"/>
@@ -51584,7 +53581,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="L47" s="1"/>
@@ -51736,7 +53733,7 @@
         <v>0.5</v>
       </c>
       <c r="I50" s="15">
-        <f t="shared" ref="I50" si="6">G50-H50</f>
+        <f t="shared" ref="I50" si="8">G50-H50</f>
         <v>-0.5</v>
       </c>
       <c r="K50" s="2"/>
@@ -51904,7 +53901,7 @@
         <v>1.25</v>
       </c>
       <c r="I53" s="15">
-        <f t="shared" ref="I53" si="7">G53-H53</f>
+        <f t="shared" ref="I53" si="9">G53-H53</f>
         <v>-0.75</v>
       </c>
       <c r="K53" s="2"/>
@@ -51993,7 +53990,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E55" s="18">
-        <f>D55/C55</f>
+        <f t="shared" ref="E55:E60" si="10">D55/C55</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F55" s="18">
@@ -52006,7 +54003,7 @@
         <v>1.5</v>
       </c>
       <c r="I55" s="15">
-        <f t="shared" ref="I55:I60" si="8">G55-H55</f>
+        <f t="shared" ref="I55:I60" si="11">G55-H55</f>
         <v>-1</v>
       </c>
       <c r="K55" s="2"/>
@@ -52077,7 +54074,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E56" s="18">
-        <f>D56/C56</f>
+        <f t="shared" si="10"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F56" s="18">
@@ -52090,7 +54087,7 @@
         <v>1.25</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-1.25</v>
       </c>
       <c r="K56" s="2"/>
@@ -52165,7 +54162,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E57" s="18">
-        <f>D57/C57</f>
+        <f t="shared" si="10"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F57" s="18">
@@ -52178,7 +54175,7 @@
         <v>4.75</v>
       </c>
       <c r="I57" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-3.5</v>
       </c>
       <c r="K57" s="2"/>
@@ -52253,7 +54250,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E58" s="18">
-        <f>D58/C58</f>
+        <f t="shared" si="10"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F58" s="18">
@@ -52266,7 +54263,7 @@
         <v>2</v>
       </c>
       <c r="I58" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-0.75</v>
       </c>
       <c r="J58" s="1"/>
@@ -52351,7 +54348,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E59" s="18">
-        <f>D59/C59</f>
+        <f t="shared" si="10"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F59" s="18">
@@ -52364,7 +54361,7 @@
         <v>7.25</v>
       </c>
       <c r="I59" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-3.5</v>
       </c>
     </row>
@@ -52382,7 +54379,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E60" s="18">
-        <f>D60/C60</f>
+        <f t="shared" si="10"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F60" s="18">
@@ -52395,7 +54392,7 @@
         <v>4.75</v>
       </c>
       <c r="I60" s="15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-4.25</v>
       </c>
     </row>
@@ -52489,7 +54486,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="15">
-        <f t="shared" ref="I65:I67" si="9">G65-H65</f>
+        <f t="shared" ref="I65:I67" si="12">G65-H65</f>
         <v>0.25</v>
       </c>
     </row>
@@ -52519,7 +54516,7 @@
         <v>3.5</v>
       </c>
       <c r="I66" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>-3.25</v>
       </c>
     </row>
@@ -52549,7 +54546,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="15">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
     </row>
@@ -52614,7 +54611,7 @@
         <v>0.5</v>
       </c>
       <c r="I70" s="15">
-        <f t="shared" ref="I70" si="10">G70-H70</f>
+        <f t="shared" ref="I70" si="13">G70-H70</f>
         <v>-0.5</v>
       </c>
     </row>
@@ -52678,7 +54675,7 @@
         <v>1.25</v>
       </c>
       <c r="I73" s="15">
-        <f t="shared" ref="I73" si="11">G73-H73</f>
+        <f t="shared" ref="I73" si="14">G73-H73</f>
         <v>-0.75</v>
       </c>
     </row>
@@ -52725,7 +54722,7 @@
         <v>1.5</v>
       </c>
       <c r="I75" s="15">
-        <f t="shared" ref="I75:I80" si="12">G75-H75</f>
+        <f t="shared" ref="I75:I80" si="15">G75-H75</f>
         <v>-1</v>
       </c>
     </row>
@@ -52755,7 +54752,7 @@
         <v>1.25</v>
       </c>
       <c r="I76" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-1.25</v>
       </c>
     </row>
@@ -52785,7 +54782,7 @@
         <v>4.75</v>
       </c>
       <c r="I77" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-3.5</v>
       </c>
     </row>
@@ -52815,7 +54812,7 @@
         <v>1.25</v>
       </c>
       <c r="I78" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0.75</v>
       </c>
     </row>
@@ -52845,7 +54842,7 @@
         <v>7.25</v>
       </c>
       <c r="I79" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-3.5</v>
       </c>
     </row>
@@ -52875,7 +54872,7 @@
         <v>4.75</v>
       </c>
       <c r="I80" s="15">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>-4.25</v>
       </c>
     </row>
@@ -53081,7 +55078,7 @@
       <c r="J4" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="63"/>
+      <c r="K4" s="9"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="Z4" s="11" t="s">
@@ -53105,7 +55102,7 @@
       <c r="AF4" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AG4" s="65" t="s">
+      <c r="AG4" s="63" t="s">
         <v>81</v>
       </c>
       <c r="AT4" t="s">
@@ -53126,10 +55123,10 @@
       <c r="E5" s="18"/>
       <c r="F5" s="25"/>
       <c r="G5" s="15"/>
-      <c r="H5" s="66"/>
+      <c r="H5" s="64"/>
       <c r="I5" s="15"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="64"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="62"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="Z5" s="15" t="s">
@@ -53180,17 +55177,17 @@
       <c r="G6" s="15">
         <v>0.25</v>
       </c>
-      <c r="H6" s="66">
+      <c r="H6" s="64">
         <v>0</v>
       </c>
       <c r="I6" s="15">
         <f t="shared" ref="I6:I8" si="0">G6-H6</f>
         <v>0.25</v>
       </c>
-      <c r="J6" s="68">
+      <c r="J6" s="19">
         <v>-1.2333333333333301</v>
       </c>
-      <c r="K6" s="64"/>
+      <c r="K6" s="62"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="Z6" s="15" t="s">
@@ -53217,10 +55214,10 @@
       <c r="AG6" s="19">
         <v>118.5</v>
       </c>
-      <c r="AT6" s="60" t="s">
+      <c r="AT6" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AU6" s="60"/>
+      <c r="AU6" s="59"/>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
@@ -53245,17 +55242,17 @@
       <c r="G7" s="15">
         <v>0.25</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="64">
         <v>3.5</v>
       </c>
       <c r="I7" s="15">
         <f>G7-H7</f>
         <v>-3.25</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="19">
         <v>-0.233333333333333</v>
       </c>
-      <c r="K7" s="64"/>
+      <c r="K7" s="62"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="Z7" s="15" t="s">
@@ -53282,10 +55279,10 @@
       <c r="AG7" s="19">
         <v>2060.9499999999998</v>
       </c>
-      <c r="AT7" s="57" t="s">
+      <c r="AT7" t="s">
         <v>38</v>
       </c>
-      <c r="AU7" s="57">
+      <c r="AU7">
         <v>0.65636192277384597</v>
       </c>
     </row>
@@ -53312,17 +55309,17 @@
       <c r="G8" s="15">
         <v>0</v>
       </c>
-      <c r="H8" s="66">
+      <c r="H8" s="64">
         <v>0</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J8" s="68">
+      <c r="J8" s="19">
         <v>0</v>
       </c>
-      <c r="K8" s="64"/>
+      <c r="K8" s="62"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="Z8" s="15" t="s">
@@ -53349,10 +55346,10 @@
       <c r="AG8" s="19">
         <v>21</v>
       </c>
-      <c r="AT8" s="57" t="s">
+      <c r="AT8" t="s">
         <v>39</v>
       </c>
-      <c r="AU8" s="57">
+      <c r="AU8">
         <v>0.43081097366738019</v>
       </c>
     </row>
@@ -53370,10 +55367,10 @@
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
       <c r="G9" s="15"/>
-      <c r="H9" s="66"/>
+      <c r="H9" s="64"/>
       <c r="I9" s="15"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="64"/>
+      <c r="J9" s="19"/>
+      <c r="K9" s="62"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="Z9" s="15" t="s">
@@ -53400,10 +55397,10 @@
       <c r="AG9" s="19">
         <v>96.5</v>
       </c>
-      <c r="AT9" s="57" t="s">
+      <c r="AT9" t="s">
         <v>40</v>
       </c>
-      <c r="AU9" s="57">
+      <c r="AU9">
         <v>0.26818553757234598</v>
       </c>
     </row>
@@ -53421,10 +55418,10 @@
       <c r="E10" s="18"/>
       <c r="F10" s="18"/>
       <c r="G10" s="15"/>
-      <c r="H10" s="66"/>
+      <c r="H10" s="64"/>
       <c r="I10" s="15"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="64"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="62"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="Z10" s="15" t="s">
@@ -53451,10 +55448,10 @@
       <c r="AG10" s="19">
         <v>47.5</v>
       </c>
-      <c r="AT10" s="57" t="s">
+      <c r="AT10" t="s">
         <v>41</v>
       </c>
-      <c r="AU10" s="57">
+      <c r="AU10">
         <v>6.7918973959245052E-2</v>
       </c>
     </row>
@@ -53472,10 +55469,10 @@
       <c r="E11" s="18"/>
       <c r="F11" s="18"/>
       <c r="G11" s="15"/>
-      <c r="H11" s="66"/>
+      <c r="H11" s="64"/>
       <c r="I11" s="15"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="64"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="62"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="Z11" s="15" t="s">
@@ -53502,10 +55499,10 @@
       <c r="AG11" s="19">
         <v>23.5</v>
       </c>
-      <c r="AT11" s="58" t="s">
+      <c r="AT11" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AU11" s="58">
+      <c r="AU11" s="57">
         <v>10</v>
       </c>
     </row>
@@ -53523,10 +55520,10 @@
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="15"/>
-      <c r="H12" s="66"/>
+      <c r="H12" s="64"/>
       <c r="I12" s="15"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="64"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="62"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="Z12" s="15" t="s">
@@ -53577,17 +55574,17 @@
       <c r="G13" s="15">
         <v>0.5</v>
       </c>
-      <c r="H13" s="66">
+      <c r="H13" s="64">
         <v>1.25</v>
       </c>
       <c r="I13" s="15">
         <f>G13-H13</f>
         <v>-0.75</v>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="15">
         <v>-3.05</v>
       </c>
-      <c r="K13" s="64"/>
+      <c r="K13" s="62"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="Z13" s="15" t="s">
@@ -53622,7 +55619,7 @@
       <c r="A14" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="61">
+      <c r="B14" s="60">
         <v>-1.9463558010346702E-2</v>
       </c>
       <c r="C14" s="18"/>
@@ -53632,10 +55629,10 @@
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="15"/>
-      <c r="H14" s="66"/>
+      <c r="H14" s="64"/>
       <c r="I14" s="15"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="64"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="62"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="Z14" s="15" t="s">
@@ -53662,20 +55659,20 @@
       <c r="AG14" s="19">
         <v>23.5</v>
       </c>
-      <c r="AT14" s="59"/>
-      <c r="AU14" s="59" t="s">
+      <c r="AT14" s="58"/>
+      <c r="AU14" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AV14" s="59" t="s">
+      <c r="AV14" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AW14" s="59" t="s">
+      <c r="AW14" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AX14" s="59" t="s">
+      <c r="AX14" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AY14" s="59" t="s">
+      <c r="AY14" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -53693,7 +55690,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E15" s="18">
-        <f>D15/C15</f>
+        <f t="shared" ref="E15:E20" si="1">D15/C15</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F15" s="18">
@@ -53702,35 +55699,35 @@
       <c r="G15" s="15">
         <v>0.5</v>
       </c>
-      <c r="H15" s="66">
+      <c r="H15" s="64">
         <v>1.5</v>
       </c>
       <c r="I15" s="15">
-        <f>G15-H15</f>
+        <f t="shared" ref="I15:I20" si="2">G15-H15</f>
         <v>-1</v>
       </c>
-      <c r="J15" s="69">
+      <c r="J15" s="15">
         <v>-5.3</v>
       </c>
-      <c r="K15" s="64"/>
+      <c r="K15" s="62"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="AT15" s="57" t="s">
+      <c r="AT15" t="s">
         <v>44</v>
       </c>
-      <c r="AU15" s="57">
+      <c r="AU15">
         <v>2</v>
       </c>
-      <c r="AV15" s="57">
+      <c r="AV15">
         <v>2.4440523929156646E-2</v>
       </c>
-      <c r="AW15" s="57">
+      <c r="AW15">
         <v>1.2220261964578323E-2</v>
       </c>
-      <c r="AX15" s="57">
+      <c r="AX15">
         <v>2.649099575146566</v>
       </c>
-      <c r="AY15" s="57">
+      <c r="AY15">
         <v>0.13912264145903849</v>
       </c>
     </row>
@@ -53748,7 +55745,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E16" s="18">
-        <f>D16/C16</f>
+        <f t="shared" si="1"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F16" s="18">
@@ -53757,33 +55754,31 @@
       <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H16" s="66">
+      <c r="H16" s="64">
         <v>1.25</v>
       </c>
       <c r="I16" s="15">
-        <f>G16-H16</f>
+        <f t="shared" si="2"/>
         <v>-1.25</v>
       </c>
-      <c r="J16" s="69">
+      <c r="J16" s="15">
         <v>11.95</v>
       </c>
-      <c r="K16" s="64"/>
+      <c r="K16" s="62"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="AT16" s="57" t="s">
+      <c r="AT16" t="s">
         <v>45</v>
       </c>
-      <c r="AU16" s="57">
+      <c r="AU16">
         <v>7</v>
       </c>
-      <c r="AV16" s="57">
+      <c r="AV16">
         <v>3.2290909165736251E-2</v>
       </c>
-      <c r="AW16" s="57">
+      <c r="AW16">
         <v>4.6129870236766074E-3</v>
       </c>
-      <c r="AX16" s="57"/>
-      <c r="AY16" s="57"/>
     </row>
     <row r="17" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
@@ -53799,7 +55794,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E17" s="18">
-        <f>D17/C17</f>
+        <f t="shared" si="1"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F17" s="18">
@@ -53808,31 +55803,31 @@
       <c r="G17" s="15">
         <v>1.25</v>
       </c>
-      <c r="H17" s="66">
+      <c r="H17" s="64">
         <v>4.75</v>
       </c>
       <c r="I17" s="15">
-        <f>G17-H17</f>
+        <f t="shared" si="2"/>
         <v>-3.5</v>
       </c>
-      <c r="J17" s="69">
+      <c r="J17" s="15">
         <v>-6.3</v>
       </c>
-      <c r="K17" s="64"/>
+      <c r="K17" s="62"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="AT17" s="58" t="s">
+      <c r="AT17" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AU17" s="58">
+      <c r="AU17" s="57">
         <v>9</v>
       </c>
-      <c r="AV17" s="58">
+      <c r="AV17" s="57">
         <v>5.6731433094892897E-2</v>
       </c>
-      <c r="AW17" s="58"/>
-      <c r="AX17" s="58"/>
-      <c r="AY17" s="58"/>
+      <c r="AW17" s="57"/>
+      <c r="AX17" s="57"/>
+      <c r="AY17" s="57"/>
     </row>
     <row r="18" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
@@ -53848,7 +55843,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E18" s="18">
-        <f>D18/C18</f>
+        <f t="shared" si="1"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F18" s="18">
@@ -53861,13 +55856,13 @@
         <v>2</v>
       </c>
       <c r="I18" s="15">
-        <f>G18-H18</f>
+        <f t="shared" si="2"/>
         <v>-0.75</v>
       </c>
-      <c r="J18" s="69">
+      <c r="J18" s="15">
         <v>-4.3</v>
       </c>
-      <c r="K18" s="64"/>
+      <c r="K18" s="62"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
     </row>
@@ -53885,7 +55880,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E19" s="18">
-        <f>D19/C19</f>
+        <f t="shared" si="1"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F19" s="18">
@@ -53894,42 +55889,42 @@
       <c r="G19" s="15">
         <v>3.75</v>
       </c>
-      <c r="H19" s="66">
+      <c r="H19" s="64">
         <v>7.25</v>
       </c>
       <c r="I19" s="15">
-        <f>G19-H19</f>
+        <f t="shared" si="2"/>
         <v>-3.5</v>
       </c>
-      <c r="J19" s="69">
+      <c r="J19" s="15">
         <v>-8.3000000000000007</v>
       </c>
-      <c r="K19" s="64"/>
+      <c r="K19" s="62"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="AT19" s="59"/>
-      <c r="AU19" s="59" t="s">
+      <c r="AT19" s="58"/>
+      <c r="AU19" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AV19" s="59" t="s">
+      <c r="AV19" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AW19" s="59" t="s">
+      <c r="AW19" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AX19" s="59" t="s">
+      <c r="AX19" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AY19" s="59" t="s">
+      <c r="AY19" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AZ19" s="59" t="s">
+      <c r="AZ19" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="BA19" s="59" t="s">
+      <c r="BA19" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="BB19" s="59" t="s">
+      <c r="BB19" s="58" t="s">
         <v>58</v>
       </c>
     </row>
@@ -53947,7 +55942,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E20" s="18">
-        <f>D20/C20</f>
+        <f t="shared" si="1"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F20" s="18">
@@ -53956,14 +55951,14 @@
       <c r="G20" s="15">
         <v>0.5</v>
       </c>
-      <c r="H20" s="66">
+      <c r="H20" s="64">
         <v>4.75</v>
       </c>
       <c r="I20" s="15">
-        <f>G20-H20</f>
+        <f t="shared" si="2"/>
         <v>-4.25</v>
       </c>
-      <c r="J20" s="69">
+      <c r="J20" s="15">
         <v>-9.8000000000000007</v>
       </c>
       <c r="L20" s="1"/>
@@ -53975,71 +55970,71 @@
       <c r="AJ20" t="s">
         <v>34</v>
       </c>
-      <c r="AT20" s="57" t="s">
+      <c r="AT20" t="s">
         <v>47</v>
       </c>
-      <c r="AU20" s="57">
+      <c r="AU20">
         <v>7.8036882959894027E-2</v>
       </c>
-      <c r="AV20" s="57">
+      <c r="AV20">
         <v>3.6014533374310015E-2</v>
       </c>
-      <c r="AW20" s="57">
+      <c r="AW20">
         <v>2.1668164390423423</v>
       </c>
-      <c r="AX20" s="57">
+      <c r="AX20">
         <v>6.6930901071746235E-2</v>
       </c>
-      <c r="AY20" s="57">
+      <c r="AY20">
         <v>-7.1239560667971658E-3</v>
       </c>
-      <c r="AZ20" s="57">
+      <c r="AZ20">
         <v>0.16319772198658522</v>
       </c>
-      <c r="BA20" s="57">
+      <c r="BA20">
         <v>-7.1239560667971658E-3</v>
       </c>
-      <c r="BB20" s="57">
+      <c r="BB20">
         <v>0.16319772198658522</v>
       </c>
     </row>
     <row r="21" spans="1:54" x14ac:dyDescent="0.25">
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="Z21" s="60" t="s">
+      <c r="Z21" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AA21" s="60"/>
+      <c r="AA21" s="59"/>
       <c r="AI21" s="1"/>
-      <c r="AJ21" s="60" t="s">
+      <c r="AJ21" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AK21" s="60"/>
-      <c r="AT21" s="57" t="s">
+      <c r="AK21" s="59"/>
+      <c r="AT21" t="s">
         <v>32</v>
       </c>
-      <c r="AU21" s="57">
+      <c r="AU21">
         <v>1.3203268117812653E-2</v>
       </c>
-      <c r="AV21" s="57">
+      <c r="AV21">
         <v>1.3893484876541051E-2</v>
       </c>
-      <c r="AW21" s="57">
+      <c r="AW21">
         <v>0.95032083275997803</v>
       </c>
-      <c r="AX21" s="57">
+      <c r="AX21">
         <v>0.37359840342506095</v>
       </c>
-      <c r="AY21" s="57">
+      <c r="AY21">
         <v>-1.9649603160393908E-2</v>
       </c>
-      <c r="AZ21" s="57">
+      <c r="AZ21">
         <v>4.6056139396019213E-2</v>
       </c>
-      <c r="BA21" s="57">
+      <c r="BA21">
         <v>-1.9649603160393908E-2</v>
       </c>
-      <c r="BB21" s="57">
+      <c r="BB21">
         <v>4.6056139396019213E-2</v>
       </c>
     </row>
@@ -54056,44 +56051,44 @@
       <c r="K22" s="8"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="Z22" s="57" t="s">
+      <c r="Z22" t="s">
         <v>38</v>
       </c>
-      <c r="AA22" s="57">
+      <c r="AA22">
         <v>0.51694226139610178</v>
       </c>
       <c r="AI22" s="1"/>
-      <c r="AJ22" s="57" t="s">
+      <c r="AJ22" t="s">
         <v>38</v>
       </c>
-      <c r="AK22" s="57">
+      <c r="AK22">
         <v>0.36455592352963589</v>
       </c>
-      <c r="AT22" s="58" t="s">
+      <c r="AT22" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="AU22" s="58">
+      <c r="AU22" s="57">
         <v>1.3002690061220546E-5</v>
       </c>
-      <c r="AV22" s="58">
+      <c r="AV22" s="57">
         <v>8.8842575515479156E-6</v>
       </c>
-      <c r="AW22" s="58">
+      <c r="AW22" s="57">
         <v>1.4635651865985211</v>
       </c>
-      <c r="AX22" s="58">
+      <c r="AX22" s="57">
         <v>0.18671919309596385</v>
       </c>
-      <c r="AY22" s="58">
+      <c r="AY22" s="57">
         <v>-8.0052408025659929E-6</v>
       </c>
-      <c r="AZ22" s="58">
+      <c r="AZ22" s="57">
         <v>3.4010620925007084E-5</v>
       </c>
-      <c r="BA22" s="58">
+      <c r="BA22" s="57">
         <v>-8.0052408025659929E-6</v>
       </c>
-      <c r="BB22" s="58">
+      <c r="BB22" s="57">
         <v>3.4010620925007084E-5</v>
       </c>
     </row>
@@ -54111,17 +56106,17 @@
       <c r="I23" s="6"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="Z23" s="57" t="s">
+      <c r="Z23" t="s">
         <v>39</v>
       </c>
-      <c r="AA23" s="57">
+      <c r="AA23">
         <v>0.26722930161731567</v>
       </c>
       <c r="AI23" s="1"/>
-      <c r="AJ23" s="57" t="s">
+      <c r="AJ23" t="s">
         <v>39</v>
       </c>
-      <c r="AK23" s="57">
+      <c r="AK23">
         <v>0.13290102138054571</v>
       </c>
     </row>
@@ -54159,17 +56154,17 @@
       <c r="K24" s="8"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="Z24" s="57" t="s">
+      <c r="Z24" t="s">
         <v>40</v>
       </c>
-      <c r="AA24" s="57">
+      <c r="AA24">
         <v>5.7866244936548697E-2</v>
       </c>
       <c r="AI24" s="1"/>
-      <c r="AJ24" s="57" t="s">
+      <c r="AJ24" t="s">
         <v>40</v>
       </c>
-      <c r="AK24" s="57">
+      <c r="AK24">
         <v>-0.11484154393929837</v>
       </c>
       <c r="AT24" t="s">
@@ -54190,23 +56185,23 @@
       <c r="E25" s="18"/>
       <c r="F25" s="25"/>
       <c r="G25" s="15"/>
-      <c r="H25" s="66"/>
+      <c r="H25" s="64"/>
       <c r="I25" s="15"/>
-      <c r="J25" s="67"/>
+      <c r="J25" s="18"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="Z25" s="57" t="s">
+      <c r="Z25" t="s">
         <v>41</v>
       </c>
-      <c r="AA25" s="57">
+      <c r="AA25">
         <v>7.7063176169384559E-2</v>
       </c>
       <c r="AI25" s="1"/>
-      <c r="AJ25" s="57" t="s">
+      <c r="AJ25" t="s">
         <v>41</v>
       </c>
-      <c r="AK25" s="57">
+      <c r="AK25">
         <v>0.18865897427581979</v>
       </c>
     </row>
@@ -54232,36 +56227,36 @@
       <c r="G26" s="15">
         <v>0.25</v>
       </c>
-      <c r="H26" s="66">
+      <c r="H26" s="64">
         <v>0</v>
       </c>
       <c r="I26" s="15">
-        <f t="shared" ref="I26:I28" si="1">G26-H26</f>
+        <f t="shared" ref="I26:I28" si="3">G26-H26</f>
         <v>0.25</v>
       </c>
-      <c r="J26" s="68">
+      <c r="J26" s="19">
         <v>-1.2333333333333301</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="Z26" s="58" t="s">
+      <c r="Z26" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AA26" s="58">
+      <c r="AA26" s="57">
         <v>10</v>
       </c>
       <c r="AI26" s="1"/>
-      <c r="AJ26" s="58" t="s">
+      <c r="AJ26" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AK26" s="58">
+      <c r="AK26" s="57">
         <v>10</v>
       </c>
-      <c r="AT26" s="60" t="s">
+      <c r="AT26" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AU26" s="60"/>
+      <c r="AU26" s="59"/>
     </row>
     <row r="27" spans="1:54" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
@@ -54285,24 +56280,24 @@
       <c r="G27" s="15">
         <v>0.25</v>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="64">
         <v>3.5</v>
       </c>
       <c r="I27" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-3.25</v>
       </c>
-      <c r="J27" s="68">
+      <c r="J27" s="19">
         <v>-0.233333333333333</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
       <c r="AI27" s="1"/>
-      <c r="AT27" s="57" t="s">
+      <c r="AT27" t="s">
         <v>38</v>
       </c>
-      <c r="AU27" s="57">
+      <c r="AU27">
         <v>0.47380484231928244</v>
       </c>
     </row>
@@ -54328,14 +56323,14 @@
       <c r="G28" s="15">
         <v>0</v>
       </c>
-      <c r="H28" s="66">
+      <c r="H28" s="64">
         <v>0</v>
       </c>
       <c r="I28" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J28" s="68">
+      <c r="J28" s="19">
         <v>0</v>
       </c>
       <c r="K28" s="1"/>
@@ -54348,10 +56343,10 @@
       <c r="AJ28" t="s">
         <v>43</v>
       </c>
-      <c r="AT28" s="57" t="s">
+      <c r="AT28" t="s">
         <v>39</v>
       </c>
-      <c r="AU28" s="57">
+      <c r="AU28">
         <v>0.22449102860520009</v>
       </c>
     </row>
@@ -54369,49 +56364,49 @@
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="15"/>
-      <c r="H29" s="66"/>
+      <c r="H29" s="64"/>
       <c r="I29" s="15"/>
-      <c r="J29" s="68"/>
+      <c r="J29" s="19"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="Z29" s="59"/>
-      <c r="AA29" s="59" t="s">
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AB29" s="59" t="s">
+      <c r="AB29" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AC29" s="59" t="s">
+      <c r="AC29" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AD29" s="59" t="s">
+      <c r="AD29" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AE29" s="59" t="s">
+      <c r="AE29" s="58" t="s">
         <v>51</v>
       </c>
       <c r="AI29" s="1"/>
-      <c r="AJ29" s="59"/>
-      <c r="AK29" s="59" t="s">
+      <c r="AJ29" s="58"/>
+      <c r="AK29" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AL29" s="59" t="s">
+      <c r="AL29" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AM29" s="59" t="s">
+      <c r="AM29" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AN29" s="59" t="s">
+      <c r="AN29" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AO29" s="59" t="s">
+      <c r="AO29" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AT29" s="57" t="s">
+      <c r="AT29" t="s">
         <v>40</v>
       </c>
-      <c r="AU29" s="57">
+      <c r="AU29">
         <v>2.9170367781143902E-3</v>
       </c>
     </row>
@@ -54429,53 +56424,53 @@
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="15"/>
-      <c r="H30" s="66"/>
+      <c r="H30" s="64"/>
       <c r="I30" s="15"/>
-      <c r="J30" s="68"/>
+      <c r="J30" s="19"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="Z30" s="57" t="s">
+      <c r="Z30" t="s">
         <v>44</v>
       </c>
-      <c r="AA30" s="57">
+      <c r="AA30">
         <v>2</v>
       </c>
-      <c r="AB30" s="57">
+      <c r="AB30">
         <v>1.5160301245697699E-2</v>
       </c>
-      <c r="AC30" s="57">
+      <c r="AC30">
         <v>7.5801506228488497E-3</v>
       </c>
-      <c r="AD30" s="57">
+      <c r="AD30">
         <v>1.2763918613625429</v>
       </c>
-      <c r="AE30" s="57">
+      <c r="AE30">
         <v>0.33681260117928441</v>
       </c>
       <c r="AI30" s="1"/>
-      <c r="AJ30" s="57" t="s">
+      <c r="AJ30" t="s">
         <v>44</v>
       </c>
-      <c r="AK30" s="57">
+      <c r="AK30">
         <v>2</v>
       </c>
-      <c r="AL30" s="57">
+      <c r="AL30">
         <v>3.8186743296809128E-2</v>
       </c>
-      <c r="AM30" s="57">
+      <c r="AM30">
         <v>1.9093371648404564E-2</v>
       </c>
-      <c r="AN30" s="57">
+      <c r="AN30">
         <v>0.53644807144450923</v>
       </c>
-      <c r="AO30" s="57">
+      <c r="AO30">
         <v>0.60707222216915957</v>
       </c>
-      <c r="AT30" s="57" t="s">
+      <c r="AT30" t="s">
         <v>41</v>
       </c>
-      <c r="AU30" s="57">
+      <c r="AU30">
         <v>3.35539679008625E-2</v>
       </c>
     </row>
@@ -54493,45 +56488,41 @@
       <c r="E31" s="18"/>
       <c r="F31" s="18"/>
       <c r="G31" s="15"/>
-      <c r="H31" s="66"/>
+      <c r="H31" s="64"/>
       <c r="I31" s="15"/>
-      <c r="J31" s="68"/>
+      <c r="J31" s="19"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="Z31" s="57" t="s">
+      <c r="Z31" t="s">
         <v>45</v>
       </c>
-      <c r="AA31" s="57">
+      <c r="AA31">
         <v>7</v>
       </c>
-      <c r="AB31" s="57">
+      <c r="AB31">
         <v>4.1571131849195198E-2</v>
       </c>
-      <c r="AC31" s="57">
+      <c r="AC31">
         <v>5.9387331213135996E-3</v>
       </c>
-      <c r="AD31" s="57"/>
-      <c r="AE31" s="57"/>
       <c r="AI31" s="1"/>
-      <c r="AJ31" s="57" t="s">
+      <c r="AJ31" t="s">
         <v>45</v>
       </c>
-      <c r="AK31" s="57">
+      <c r="AK31">
         <v>7</v>
       </c>
-      <c r="AL31" s="57">
+      <c r="AL31">
         <v>0.24914546002363105</v>
       </c>
-      <c r="AM31" s="57">
+      <c r="AM31">
         <v>3.5592208574804433E-2</v>
       </c>
-      <c r="AN31" s="57"/>
-      <c r="AO31" s="57"/>
-      <c r="AT31" s="58" t="s">
+      <c r="AT31" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AU31" s="58">
+      <c r="AU31" s="57">
         <v>10</v>
       </c>
     </row>
@@ -54549,37 +56540,37 @@
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="15"/>
-      <c r="H32" s="66"/>
+      <c r="H32" s="64"/>
       <c r="I32" s="15"/>
-      <c r="J32" s="68"/>
+      <c r="J32" s="19"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="Z32" s="58" t="s">
+      <c r="Z32" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AA32" s="58">
+      <c r="AA32" s="57">
         <v>9</v>
       </c>
-      <c r="AB32" s="58">
+      <c r="AB32" s="57">
         <v>5.6731433094892897E-2</v>
       </c>
-      <c r="AC32" s="58"/>
-      <c r="AD32" s="58"/>
-      <c r="AE32" s="58"/>
+      <c r="AC32" s="57"/>
+      <c r="AD32" s="57"/>
+      <c r="AE32" s="57"/>
       <c r="AI32" s="1"/>
-      <c r="AJ32" s="58" t="s">
+      <c r="AJ32" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AK32" s="58">
+      <c r="AK32" s="57">
         <v>9</v>
       </c>
-      <c r="AL32" s="58">
+      <c r="AL32" s="57">
         <v>0.28733220332044018</v>
       </c>
-      <c r="AM32" s="58"/>
-      <c r="AN32" s="58"/>
-      <c r="AO32" s="58"/>
+      <c r="AM32" s="57"/>
+      <c r="AN32" s="57"/>
+      <c r="AO32" s="57"/>
     </row>
     <row r="33" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
@@ -54604,14 +56595,14 @@
       <c r="G33" s="15">
         <v>0.5</v>
       </c>
-      <c r="H33" s="66">
+      <c r="H33" s="64">
         <v>1.25</v>
       </c>
       <c r="I33" s="15">
         <f>G33-H33</f>
         <v>-0.75</v>
       </c>
-      <c r="J33" s="69">
+      <c r="J33" s="15">
         <v>-3.05</v>
       </c>
       <c r="K33" s="1"/>
@@ -54636,77 +56627,77 @@
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="15"/>
-      <c r="H34" s="66"/>
+      <c r="H34" s="64"/>
       <c r="I34" s="15"/>
-      <c r="J34" s="68"/>
+      <c r="J34" s="19"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="Z34" s="59"/>
-      <c r="AA34" s="59" t="s">
+      <c r="Z34" s="58"/>
+      <c r="AA34" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AB34" s="59" t="s">
+      <c r="AB34" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AC34" s="59" t="s">
+      <c r="AC34" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AD34" s="59" t="s">
+      <c r="AD34" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AE34" s="59" t="s">
+      <c r="AE34" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AF34" s="59" t="s">
+      <c r="AF34" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AG34" s="59" t="s">
+      <c r="AG34" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AH34" s="59" t="s">
+      <c r="AH34" s="58" t="s">
         <v>58</v>
       </c>
       <c r="AI34" s="1"/>
-      <c r="AJ34" s="59"/>
-      <c r="AK34" s="59" t="s">
+      <c r="AJ34" s="58"/>
+      <c r="AK34" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AL34" s="59" t="s">
+      <c r="AL34" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AM34" s="59" t="s">
+      <c r="AM34" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AN34" s="59" t="s">
+      <c r="AN34" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AO34" s="59" t="s">
+      <c r="AO34" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AP34" s="59" t="s">
+      <c r="AP34" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AQ34" s="59" t="s">
+      <c r="AQ34" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AR34" s="59" t="s">
+      <c r="AR34" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AT34" s="59"/>
-      <c r="AU34" s="59" t="s">
+      <c r="AT34" s="58"/>
+      <c r="AU34" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AV34" s="59" t="s">
+      <c r="AV34" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AW34" s="59" t="s">
+      <c r="AW34" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AX34" s="59" t="s">
+      <c r="AX34" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AY34" s="59" t="s">
+      <c r="AY34" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -54724,7 +56715,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E35" s="18">
-        <f>D35/C35</f>
+        <f t="shared" ref="E35:E40" si="4">D35/C35</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F35" s="18">
@@ -54733,90 +56724,90 @@
       <c r="G35" s="15">
         <v>0.5</v>
       </c>
-      <c r="H35" s="66">
+      <c r="H35" s="64">
         <v>1.5</v>
       </c>
       <c r="I35" s="15">
-        <f>G35-H35</f>
+        <f t="shared" ref="I35:I40" si="5">G35-H35</f>
         <v>-1</v>
       </c>
-      <c r="J35" s="69">
+      <c r="J35" s="15">
         <v>-5.3</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="Z35" s="57" t="s">
+      <c r="Z35" t="s">
         <v>47</v>
       </c>
-      <c r="AA35" s="57">
+      <c r="AA35">
         <v>-7.2141295442709641E-2</v>
       </c>
-      <c r="AB35" s="57">
+      <c r="AB35">
         <v>0.5665371020397747</v>
       </c>
-      <c r="AC35" s="57">
+      <c r="AC35">
         <v>-0.12733728326524471</v>
       </c>
-      <c r="AD35" s="57">
+      <c r="AD35">
         <v>0.9022542431883902</v>
       </c>
-      <c r="AE35" s="57">
+      <c r="AE35">
         <v>-1.411788666353057</v>
       </c>
-      <c r="AF35" s="57">
+      <c r="AF35">
         <v>1.2675060754676377</v>
       </c>
-      <c r="AG35" s="57">
+      <c r="AG35">
         <v>-1.411788666353057</v>
       </c>
-      <c r="AH35" s="57">
+      <c r="AH35">
         <v>1.2675060754676377</v>
       </c>
       <c r="AI35" s="1"/>
-      <c r="AJ35" s="57" t="s">
+      <c r="AJ35" t="s">
         <v>47</v>
       </c>
-      <c r="AK35" s="57">
+      <c r="AK35">
         <v>-1.1384414476301981</v>
       </c>
-      <c r="AL35" s="57">
+      <c r="AL35">
         <v>1.3869439837918496</v>
       </c>
-      <c r="AM35" s="57">
+      <c r="AM35">
         <v>-0.82082727271922296</v>
       </c>
-      <c r="AN35" s="57">
+      <c r="AN35">
         <v>0.43880001735556717</v>
       </c>
-      <c r="AO35" s="57">
+      <c r="AO35">
         <v>-4.4180428273051158</v>
       </c>
-      <c r="AP35" s="57">
+      <c r="AP35">
         <v>2.1411599320447197</v>
       </c>
-      <c r="AQ35" s="57">
+      <c r="AQ35">
         <v>-4.4180428273051158</v>
       </c>
-      <c r="AR35" s="57">
+      <c r="AR35">
         <v>2.1411599320447197</v>
       </c>
-      <c r="AT35" s="57" t="s">
+      <c r="AT35" t="s">
         <v>44</v>
       </c>
-      <c r="AU35" s="57">
+      <c r="AU35">
         <v>2</v>
       </c>
-      <c r="AV35" s="57">
+      <c r="AV35">
         <v>2.2813818025074432E-3</v>
       </c>
-      <c r="AW35" s="57">
+      <c r="AW35">
         <v>1.1406909012537216E-3</v>
       </c>
-      <c r="AX35" s="57">
+      <c r="AX35">
         <v>1.013165068490488</v>
       </c>
-      <c r="AY35" s="57">
+      <c r="AY35">
         <v>0.41072760422250654</v>
       </c>
     </row>
@@ -54834,7 +56825,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E36" s="18">
-        <f>D36/C36</f>
+        <f t="shared" si="4"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F36" s="18">
@@ -54843,88 +56834,86 @@
       <c r="G36" s="15">
         <v>0</v>
       </c>
-      <c r="H36" s="66">
+      <c r="H36" s="64">
         <v>1.25</v>
       </c>
       <c r="I36" s="15">
-        <f>G36-H36</f>
+        <f t="shared" si="5"/>
         <v>-1.25</v>
       </c>
-      <c r="J36" s="69">
+      <c r="J36" s="15">
         <v>11.95</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="Z36" s="57" t="s">
+      <c r="Z36" t="s">
         <v>62</v>
       </c>
-      <c r="AA36" s="57">
+      <c r="AA36">
         <v>0.17005375973979706</v>
       </c>
-      <c r="AB36" s="57">
+      <c r="AB36">
         <v>0.53460296487606895</v>
       </c>
-      <c r="AC36" s="57">
+      <c r="AC36">
         <v>0.3180935589820732</v>
       </c>
-      <c r="AD36" s="57">
+      <c r="AD36">
         <v>0.7596936034157481</v>
       </c>
-      <c r="AE36" s="57">
+      <c r="AE36">
         <v>-1.0940813759795613</v>
       </c>
-      <c r="AF36" s="57">
+      <c r="AF36">
         <v>1.4341888954591555</v>
       </c>
-      <c r="AG36" s="57">
+      <c r="AG36">
         <v>-1.0940813759795613</v>
       </c>
-      <c r="AH36" s="57">
+      <c r="AH36">
         <v>1.4341888954591555</v>
       </c>
       <c r="AI36" s="1"/>
-      <c r="AJ36" s="57" t="s">
+      <c r="AJ36" t="s">
         <v>62</v>
       </c>
-      <c r="AK36" s="57">
+      <c r="AK36">
         <v>1.0494670872407263</v>
       </c>
-      <c r="AL36" s="57">
+      <c r="AL36">
         <v>1.3087657687070484</v>
       </c>
-      <c r="AM36" s="57">
+      <c r="AM36">
         <v>0.80187540989669404</v>
       </c>
-      <c r="AN36" s="57">
+      <c r="AN36">
         <v>0.44898585462803231</v>
       </c>
-      <c r="AO36" s="57">
+      <c r="AO36">
         <v>-2.0452721890984336</v>
       </c>
-      <c r="AP36" s="57">
+      <c r="AP36">
         <v>4.1442063635798867</v>
       </c>
-      <c r="AQ36" s="57">
+      <c r="AQ36">
         <v>-2.0452721890984336</v>
       </c>
-      <c r="AR36" s="57">
+      <c r="AR36">
         <v>4.1442063635798867</v>
       </c>
-      <c r="AT36" s="57" t="s">
+      <c r="AT36" t="s">
         <v>45</v>
       </c>
-      <c r="AU36" s="57">
+      <c r="AU36">
         <v>7</v>
       </c>
-      <c r="AV36" s="57">
+      <c r="AV36">
         <v>7.8810813332447771E-3</v>
       </c>
-      <c r="AW36" s="57">
+      <c r="AW36">
         <v>1.125868761892111E-3</v>
       </c>
-      <c r="AX36" s="57"/>
-      <c r="AY36" s="57"/>
     </row>
     <row r="37" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
@@ -54940,7 +56929,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E37" s="18">
-        <f>D37/C37</f>
+        <f t="shared" si="4"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F37" s="18">
@@ -54949,86 +56938,86 @@
       <c r="G37" s="15">
         <v>1.25</v>
       </c>
-      <c r="H37" s="66">
+      <c r="H37" s="64">
         <v>4.75</v>
       </c>
       <c r="I37" s="15">
-        <f>G37-H37</f>
+        <f t="shared" si="5"/>
         <v>-3.5</v>
       </c>
-      <c r="J37" s="69">
+      <c r="J37" s="15">
         <v>-6.3</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="Z37" s="58" t="s">
+      <c r="Z37" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="AA37" s="58">
+      <c r="AA37" s="57">
         <v>2.094648600458297E-2</v>
       </c>
-      <c r="AB37" s="58">
+      <c r="AB37" s="57">
         <v>1.4657276674798667E-2</v>
       </c>
-      <c r="AC37" s="58">
+      <c r="AC37" s="57">
         <v>1.4290844383525763</v>
       </c>
-      <c r="AD37" s="58">
+      <c r="AD37" s="57">
         <v>0.19604882381200342</v>
       </c>
-      <c r="AE37" s="58">
+      <c r="AE37" s="57">
         <v>-1.3712465882951209E-2</v>
       </c>
-      <c r="AF37" s="58">
+      <c r="AF37" s="57">
         <v>5.5605437892117152E-2</v>
       </c>
-      <c r="AG37" s="58">
+      <c r="AG37" s="57">
         <v>-1.3712465882951209E-2</v>
       </c>
-      <c r="AH37" s="58">
+      <c r="AH37" s="57">
         <v>5.5605437892117152E-2</v>
       </c>
       <c r="AI37" s="1"/>
-      <c r="AJ37" s="58" t="s">
+      <c r="AJ37" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="AK37" s="58">
+      <c r="AK37" s="57">
         <v>1.523088215905319E-2</v>
       </c>
-      <c r="AL37" s="58">
+      <c r="AL37" s="57">
         <v>3.588259556115956E-2</v>
       </c>
-      <c r="AM37" s="58">
+      <c r="AM37" s="57">
         <v>0.42446433767850317</v>
       </c>
-      <c r="AN37" s="58">
+      <c r="AN37" s="57">
         <v>0.6839682584636908</v>
       </c>
-      <c r="AO37" s="58">
+      <c r="AO37" s="57">
         <v>-6.9617973514960324E-2</v>
       </c>
-      <c r="AP37" s="58">
+      <c r="AP37" s="57">
         <v>0.1000797378330667</v>
       </c>
-      <c r="AQ37" s="58">
+      <c r="AQ37" s="57">
         <v>-6.9617973514960324E-2</v>
       </c>
-      <c r="AR37" s="58">
+      <c r="AR37" s="57">
         <v>0.1000797378330667</v>
       </c>
-      <c r="AT37" s="58" t="s">
+      <c r="AT37" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AU37" s="58">
+      <c r="AU37" s="57">
         <v>9</v>
       </c>
-      <c r="AV37" s="58">
+      <c r="AV37" s="57">
         <v>1.016246313575222E-2</v>
       </c>
-      <c r="AW37" s="58"/>
-      <c r="AX37" s="58"/>
-      <c r="AY37" s="58"/>
+      <c r="AW37" s="57"/>
+      <c r="AX37" s="57"/>
+      <c r="AY37" s="57"/>
     </row>
     <row r="38" spans="1:54" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
@@ -55044,7 +57033,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E38" s="18">
-        <f>D38/C38</f>
+        <f t="shared" si="4"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F38" s="18">
@@ -55057,10 +57046,10 @@
         <v>2</v>
       </c>
       <c r="I38" s="15">
-        <f>G38-H38</f>
+        <f t="shared" si="5"/>
         <v>-0.75</v>
       </c>
-      <c r="J38" s="69">
+      <c r="J38" s="15">
         <v>-4.3</v>
       </c>
       <c r="K38" s="1"/>
@@ -55082,7 +57071,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E39" s="18">
-        <f>D39/C39</f>
+        <f t="shared" si="4"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F39" s="18">
@@ -55091,43 +57080,43 @@
       <c r="G39" s="15">
         <v>3.75</v>
       </c>
-      <c r="H39" s="66">
+      <c r="H39" s="64">
         <v>7.25</v>
       </c>
       <c r="I39" s="15">
-        <f>G39-H39</f>
+        <f t="shared" si="5"/>
         <v>-3.5</v>
       </c>
-      <c r="J39" s="69">
+      <c r="J39" s="15">
         <v>-8.3000000000000007</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="AI39" s="1"/>
-      <c r="AT39" s="59"/>
-      <c r="AU39" s="59" t="s">
+      <c r="AT39" s="58"/>
+      <c r="AU39" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AV39" s="59" t="s">
+      <c r="AV39" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AW39" s="59" t="s">
+      <c r="AW39" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AX39" s="59" t="s">
+      <c r="AX39" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AY39" s="59" t="s">
+      <c r="AY39" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AZ39" s="59" t="s">
+      <c r="AZ39" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="BA39" s="59" t="s">
+      <c r="BA39" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="BB39" s="59" t="s">
+      <c r="BB39" s="58" t="s">
         <v>58</v>
       </c>
     </row>
@@ -55145,7 +57134,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E40" s="18">
-        <f>D40/C40</f>
+        <f t="shared" si="4"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F40" s="18">
@@ -55154,14 +57143,14 @@
       <c r="G40" s="15">
         <v>0.5</v>
       </c>
-      <c r="H40" s="66">
+      <c r="H40" s="64">
         <v>4.75</v>
       </c>
       <c r="I40" s="15">
-        <f>G40-H40</f>
+        <f t="shared" si="5"/>
         <v>-4.25</v>
       </c>
-      <c r="J40" s="69">
+      <c r="J40" s="15">
         <v>-9.8000000000000007</v>
       </c>
       <c r="K40" s="1"/>
@@ -55174,31 +57163,31 @@
       <c r="AJ40" t="s">
         <v>80</v>
       </c>
-      <c r="AT40" s="57" t="s">
+      <c r="AT40" t="s">
         <v>47</v>
       </c>
-      <c r="AU40" s="57">
+      <c r="AU40">
         <v>0.1128250068170468</v>
       </c>
-      <c r="AV40" s="57">
+      <c r="AV40">
         <v>1.7792237225657464E-2</v>
       </c>
-      <c r="AW40" s="57">
+      <c r="AW40">
         <v>6.341249016978395</v>
       </c>
-      <c r="AX40" s="57">
+      <c r="AX40">
         <v>3.8846998688098645E-4</v>
       </c>
-      <c r="AY40" s="57">
+      <c r="AY40">
         <v>7.075305118316523E-2</v>
       </c>
-      <c r="AZ40" s="57">
+      <c r="AZ40">
         <v>0.15489696245092838</v>
       </c>
-      <c r="BA40" s="57">
+      <c r="BA40">
         <v>7.075305118316523E-2</v>
       </c>
-      <c r="BB40" s="57">
+      <c r="BB40">
         <v>0.15489696245092838</v>
       </c>
     </row>
@@ -55207,40 +57196,40 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
-      <c r="Z41" s="60" t="s">
+      <c r="Z41" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AA41" s="60"/>
+      <c r="AA41" s="59"/>
       <c r="AI41" s="1"/>
-      <c r="AJ41" s="60" t="s">
+      <c r="AJ41" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AK41" s="60"/>
-      <c r="AT41" s="57" t="s">
+      <c r="AK41" s="59"/>
+      <c r="AT41" t="s">
         <v>32</v>
       </c>
-      <c r="AU41" s="57">
+      <c r="AU41">
         <v>6.0565857359490714E-3</v>
       </c>
-      <c r="AV41" s="57">
+      <c r="AV41">
         <v>6.8637895775385295E-3</v>
       </c>
-      <c r="AW41" s="57">
+      <c r="AW41">
         <v>0.88239676748963869</v>
       </c>
-      <c r="AX41" s="57">
+      <c r="AX41">
         <v>0.40684155545085693</v>
       </c>
-      <c r="AY41" s="57">
+      <c r="AY41">
         <v>-1.0173697556928329E-2</v>
       </c>
-      <c r="AZ41" s="57">
+      <c r="AZ41">
         <v>2.2286869028826473E-2</v>
       </c>
-      <c r="BA41" s="57">
+      <c r="BA41">
         <v>-1.0173697556928329E-2</v>
       </c>
-      <c r="BB41" s="57">
+      <c r="BB41">
         <v>2.2286869028826473E-2</v>
       </c>
     </row>
@@ -55249,44 +57238,44 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
-      <c r="Z42" s="57" t="s">
+      <c r="Z42" t="s">
         <v>38</v>
       </c>
-      <c r="AA42" s="57">
+      <c r="AA42">
         <v>0.43767123618496118</v>
       </c>
       <c r="AI42" s="1"/>
-      <c r="AJ42" s="57" t="s">
+      <c r="AJ42" t="s">
         <v>38</v>
       </c>
-      <c r="AK42" s="57">
+      <c r="AK42">
         <v>0.44220732352193126</v>
       </c>
-      <c r="AT42" s="58" t="s">
+      <c r="AT42" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="AU42" s="58">
+      <c r="AU42" s="57">
         <v>2.6956281748751023E-6</v>
       </c>
-      <c r="AV42" s="58">
+      <c r="AV42" s="57">
         <v>4.3890841591115744E-6</v>
       </c>
-      <c r="AW42" s="58">
+      <c r="AW42" s="57">
         <v>0.61416643590191344</v>
       </c>
-      <c r="AX42" s="58">
+      <c r="AX42" s="57">
         <v>0.55852959554807313</v>
       </c>
-      <c r="AY42" s="58">
+      <c r="AY42" s="57">
         <v>-7.6829066700418523E-6</v>
       </c>
-      <c r="AZ42" s="58">
+      <c r="AZ42" s="57">
         <v>1.3074163019792056E-5</v>
       </c>
-      <c r="BA42" s="58">
+      <c r="BA42" s="57">
         <v>-7.6829066700418523E-6</v>
       </c>
-      <c r="BB42" s="58">
+      <c r="BB42" s="57">
         <v>1.3074163019792056E-5</v>
       </c>
     </row>
@@ -55324,17 +57313,17 @@
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
-      <c r="Z43" s="57" t="s">
+      <c r="Z43" t="s">
         <v>39</v>
       </c>
-      <c r="AA43" s="57">
+      <c r="AA43">
         <v>0.19155611098367209</v>
       </c>
       <c r="AI43" s="1"/>
-      <c r="AJ43" s="57" t="s">
+      <c r="AJ43" t="s">
         <v>39</v>
       </c>
-      <c r="AK43" s="57">
+      <c r="AK43">
         <v>0.19554731697642999</v>
       </c>
     </row>
@@ -55354,21 +57343,21 @@
       <c r="G44" s="15"/>
       <c r="H44" s="15"/>
       <c r="I44" s="15"/>
-      <c r="J44" s="67"/>
+      <c r="J44" s="18"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
-      <c r="Z44" s="57" t="s">
+      <c r="Z44" t="s">
         <v>40</v>
       </c>
-      <c r="AA44" s="57">
+      <c r="AA44">
         <v>-3.9427857306707316E-2</v>
       </c>
       <c r="AI44" s="1"/>
-      <c r="AJ44" s="57" t="s">
+      <c r="AJ44" t="s">
         <v>40</v>
       </c>
-      <c r="AK44" s="57">
+      <c r="AK44">
         <v>-3.429630674459002E-2</v>
       </c>
     </row>
@@ -55398,26 +57387,26 @@
         <v>0</v>
       </c>
       <c r="I45" s="15">
-        <f t="shared" ref="I45:I47" si="2">G45-H45</f>
+        <f t="shared" ref="I45:I47" si="6">G45-H45</f>
         <v>0.25</v>
       </c>
-      <c r="J45" s="68">
+      <c r="J45" s="19">
         <v>-1.2333333333333301</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
-      <c r="Z45" s="57" t="s">
+      <c r="Z45" t="s">
         <v>41</v>
       </c>
-      <c r="AA45" s="57">
+      <c r="AA45">
         <v>3.4259057654149952E-2</v>
       </c>
       <c r="AI45" s="1"/>
-      <c r="AJ45" s="57" t="s">
+      <c r="AJ45" t="s">
         <v>41</v>
       </c>
-      <c r="AK45" s="57">
+      <c r="AK45">
         <v>0.2246168012952178</v>
       </c>
     </row>
@@ -55447,10 +57436,10 @@
         <v>3.5</v>
       </c>
       <c r="I46" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>-3.25</v>
       </c>
-      <c r="J46" s="68">
+      <c r="J46" s="19">
         <v>-0.233333333333333</v>
       </c>
       <c r="K46" s="1"/>
@@ -55467,17 +57456,17 @@
       <c r="V46" s="1"/>
       <c r="W46" s="1"/>
       <c r="X46" s="1"/>
-      <c r="Z46" s="58" t="s">
+      <c r="Z46" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AA46" s="58">
+      <c r="AA46" s="57">
         <v>10</v>
       </c>
       <c r="AI46" s="1"/>
-      <c r="AJ46" s="58" t="s">
+      <c r="AJ46" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AK46" s="58">
+      <c r="AK46" s="57">
         <v>10</v>
       </c>
     </row>
@@ -55508,10 +57497,10 @@
         <v>0</v>
       </c>
       <c r="I47" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J47" s="68">
+      <c r="J47" s="19">
         <v>0</v>
       </c>
       <c r="M47" s="1"/>
@@ -55534,7 +57523,7 @@
       <c r="G48" s="15"/>
       <c r="H48" s="15"/>
       <c r="I48" s="15"/>
-      <c r="J48" s="68"/>
+      <c r="J48" s="19"/>
       <c r="L48" s="2"/>
       <c r="M48" s="1"/>
       <c r="X48" s="1"/>
@@ -55561,40 +57550,40 @@
       <c r="G49" s="15"/>
       <c r="H49" s="15"/>
       <c r="I49" s="15"/>
-      <c r="J49" s="68"/>
+      <c r="J49" s="19"/>
       <c r="L49" s="2"/>
       <c r="M49" s="1"/>
       <c r="X49" s="1"/>
-      <c r="Z49" s="59"/>
-      <c r="AA49" s="59" t="s">
+      <c r="Z49" s="58"/>
+      <c r="AA49" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AB49" s="59" t="s">
+      <c r="AB49" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AC49" s="59" t="s">
+      <c r="AC49" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AD49" s="59" t="s">
+      <c r="AD49" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AE49" s="59" t="s">
+      <c r="AE49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AJ49" s="59"/>
-      <c r="AK49" s="59" t="s">
+      <c r="AJ49" s="58"/>
+      <c r="AK49" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AL49" s="59" t="s">
+      <c r="AL49" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AM49" s="59" t="s">
+      <c r="AM49" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AN49" s="59" t="s">
+      <c r="AN49" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AO49" s="59" t="s">
+      <c r="AO49" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -55614,44 +57603,44 @@
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
       <c r="I50" s="15"/>
-      <c r="J50" s="68"/>
+      <c r="J50" s="19"/>
       <c r="L50" s="2"/>
       <c r="M50" s="1"/>
       <c r="X50" s="1"/>
-      <c r="Z50" s="57" t="s">
+      <c r="Z50" t="s">
         <v>44</v>
       </c>
-      <c r="AA50" s="57">
+      <c r="AA50">
         <v>2</v>
       </c>
-      <c r="AB50" s="57">
+      <c r="AB50">
         <v>1.9466819162996286E-3</v>
       </c>
-      <c r="AC50" s="57">
+      <c r="AC50">
         <v>9.7334095814981432E-4</v>
       </c>
-      <c r="AD50" s="57">
+      <c r="AD50">
         <v>0.82930478855943401</v>
       </c>
-      <c r="AE50" s="57">
+      <c r="AE50">
         <v>0.47508857768394674</v>
       </c>
-      <c r="AJ50" s="57" t="s">
+      <c r="AJ50" t="s">
         <v>44</v>
       </c>
-      <c r="AK50" s="57">
+      <c r="AK50">
         <v>2</v>
       </c>
-      <c r="AL50" s="57">
+      <c r="AL50">
         <v>8.5848729769016308E-2</v>
       </c>
-      <c r="AM50" s="57">
+      <c r="AM50">
         <v>4.2924364884508154E-2</v>
       </c>
-      <c r="AN50" s="57">
+      <c r="AN50">
         <v>0.85078417147556695</v>
       </c>
-      <c r="AO50" s="57">
+      <c r="AO50">
         <v>0.46692998676722636</v>
       </c>
     </row>
@@ -55671,38 +57660,34 @@
       <c r="G51" s="15"/>
       <c r="H51" s="15"/>
       <c r="I51" s="15"/>
-      <c r="J51" s="68"/>
+      <c r="J51" s="19"/>
       <c r="L51" s="2"/>
       <c r="M51" s="1"/>
       <c r="X51" s="1"/>
-      <c r="Z51" s="57" t="s">
+      <c r="Z51" t="s">
         <v>45</v>
       </c>
-      <c r="AA51" s="57">
+      <c r="AA51">
         <v>7</v>
       </c>
-      <c r="AB51" s="57">
+      <c r="AB51">
         <v>8.2157812194525916E-3</v>
       </c>
-      <c r="AC51" s="57">
+      <c r="AC51">
         <v>1.1736830313503702E-3</v>
       </c>
-      <c r="AD51" s="57"/>
-      <c r="AE51" s="57"/>
-      <c r="AJ51" s="57" t="s">
+      <c r="AJ51" t="s">
         <v>45</v>
       </c>
-      <c r="AK51" s="57">
+      <c r="AK51">
         <v>7</v>
       </c>
-      <c r="AL51" s="57">
+      <c r="AL51">
         <v>0.35316895196866749</v>
       </c>
-      <c r="AM51" s="57">
+      <c r="AM51">
         <v>5.0452707424095355E-2</v>
       </c>
-      <c r="AN51" s="57"/>
-      <c r="AO51" s="57"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
@@ -55731,39 +57716,39 @@
         <v>1.25</v>
       </c>
       <c r="I52" s="15">
-        <f t="shared" ref="I52" si="3">G52-H52</f>
+        <f t="shared" ref="I52" si="7">G52-H52</f>
         <v>-0.75</v>
       </c>
-      <c r="J52" s="69">
+      <c r="J52" s="15">
         <v>-3.05</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Z52" s="58" t="s">
+      <c r="Z52" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AA52" s="58">
+      <c r="AA52" s="57">
         <v>9</v>
       </c>
-      <c r="AB52" s="58">
+      <c r="AB52" s="57">
         <v>1.016246313575222E-2</v>
       </c>
-      <c r="AC52" s="58"/>
-      <c r="AD52" s="58"/>
-      <c r="AE52" s="58"/>
-      <c r="AJ52" s="58" t="s">
+      <c r="AC52" s="57"/>
+      <c r="AD52" s="57"/>
+      <c r="AE52" s="57"/>
+      <c r="AJ52" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AK52" s="58">
+      <c r="AK52" s="57">
         <v>9</v>
       </c>
-      <c r="AL52" s="58">
+      <c r="AL52" s="57">
         <v>0.4390176817376838</v>
       </c>
-      <c r="AM52" s="58"/>
-      <c r="AN52" s="58"/>
-      <c r="AO52" s="58"/>
+      <c r="AM52" s="57"/>
+      <c r="AN52" s="57"/>
+      <c r="AO52" s="57"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
@@ -55781,7 +57766,7 @@
       <c r="G53" s="15"/>
       <c r="H53" s="15"/>
       <c r="I53" s="15"/>
-      <c r="J53" s="68"/>
+      <c r="J53" s="19"/>
       <c r="L53" s="2"/>
       <c r="M53" s="1"/>
       <c r="X53" s="1"/>
@@ -55800,7 +57785,7 @@
         <v>115.360934813333</v>
       </c>
       <c r="E54" s="18">
-        <f>D54/C54</f>
+        <f t="shared" ref="E54:E59" si="8">D54/C54</f>
         <v>1.0331150820718804</v>
       </c>
       <c r="F54" s="18">
@@ -55813,63 +57798,63 @@
         <v>1.5</v>
       </c>
       <c r="I54" s="15">
-        <f t="shared" ref="I54:I59" si="4">G54-H54</f>
+        <f t="shared" ref="I54:I59" si="9">G54-H54</f>
         <v>-1</v>
       </c>
-      <c r="J54" s="69">
+      <c r="J54" s="15">
         <v>-5.3</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" s="1"/>
       <c r="X54" s="1"/>
-      <c r="Z54" s="59"/>
-      <c r="AA54" s="59" t="s">
+      <c r="Z54" s="58"/>
+      <c r="AA54" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AB54" s="59" t="s">
+      <c r="AB54" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AC54" s="59" t="s">
+      <c r="AC54" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AD54" s="59" t="s">
+      <c r="AD54" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AE54" s="59" t="s">
+      <c r="AE54" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AF54" s="59" t="s">
+      <c r="AF54" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AG54" s="59" t="s">
+      <c r="AG54" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AH54" s="59" t="s">
+      <c r="AH54" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AJ54" s="59"/>
-      <c r="AK54" s="59" t="s">
+      <c r="AJ54" s="58"/>
+      <c r="AK54" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AL54" s="59" t="s">
+      <c r="AL54" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AM54" s="59" t="s">
+      <c r="AM54" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AN54" s="59" t="s">
+      <c r="AN54" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AO54" s="59" t="s">
+      <c r="AO54" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AP54" s="59" t="s">
+      <c r="AP54" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AQ54" s="59" t="s">
+      <c r="AQ54" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AR54" s="59" t="s">
+      <c r="AR54" s="58" t="s">
         <v>58</v>
       </c>
     </row>
@@ -55887,7 +57872,7 @@
         <v>118.05576815000001</v>
       </c>
       <c r="E55" s="18">
-        <f>D55/C55</f>
+        <f t="shared" si="8"/>
         <v>1.0275460447393339</v>
       </c>
       <c r="F55" s="18">
@@ -55900,67 +57885,67 @@
         <v>1.25</v>
       </c>
       <c r="I55" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-1.25</v>
       </c>
-      <c r="J55" s="69">
+      <c r="J55" s="15">
         <v>11.95</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" s="1"/>
       <c r="X55" s="1"/>
-      <c r="Z55" s="57" t="s">
+      <c r="Z55" t="s">
         <v>47</v>
       </c>
-      <c r="AA55" s="57">
+      <c r="AA55">
         <v>4.9373958987233797E-2</v>
       </c>
-      <c r="AB55" s="57">
+      <c r="AB55">
         <v>0.25185864646085582</v>
       </c>
-      <c r="AC55" s="57">
+      <c r="AC55">
         <v>0.19603837184484973</v>
       </c>
-      <c r="AD55" s="57">
+      <c r="AD55">
         <v>0.85014973302517838</v>
       </c>
-      <c r="AE55" s="57">
+      <c r="AE55">
         <v>-0.54617710440743916</v>
       </c>
-      <c r="AF55" s="57">
+      <c r="AF55">
         <v>0.64492502238190685</v>
       </c>
-      <c r="AG55" s="57">
+      <c r="AG55">
         <v>-0.54617710440743916</v>
       </c>
-      <c r="AH55" s="57">
+      <c r="AH55">
         <v>0.64492502238190685</v>
       </c>
-      <c r="AJ55" s="57" t="s">
+      <c r="AJ55" t="s">
         <v>47</v>
       </c>
-      <c r="AK55" s="57">
+      <c r="AK55">
         <v>1.9032809403152653</v>
       </c>
-      <c r="AL55" s="57">
+      <c r="AL55">
         <v>1.6512912911288959</v>
       </c>
-      <c r="AM55" s="57">
+      <c r="AM55">
         <v>1.1526015734111321</v>
       </c>
-      <c r="AN55" s="57">
+      <c r="AN55">
         <v>0.28691068167195516</v>
       </c>
-      <c r="AO55" s="57">
+      <c r="AO55">
         <v>-2.0014024931320837</v>
       </c>
-      <c r="AP55" s="57">
+      <c r="AP55">
         <v>5.8079643737626139</v>
       </c>
-      <c r="AQ55" s="57">
+      <c r="AQ55">
         <v>-2.0014024931320837</v>
       </c>
-      <c r="AR55" s="57">
+      <c r="AR55">
         <v>5.8079643737626139</v>
       </c>
     </row>
@@ -55978,7 +57963,7 @@
         <v>119.77022043333299</v>
       </c>
       <c r="E56" s="18">
-        <f>D56/C56</f>
+        <f t="shared" si="8"/>
         <v>1.0275826446035865</v>
       </c>
       <c r="F56" s="18">
@@ -55991,67 +57976,67 @@
         <v>4.75</v>
       </c>
       <c r="I56" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-3.5</v>
       </c>
-      <c r="J56" s="69">
+      <c r="J56" s="15">
         <v>-6.3</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" s="1"/>
       <c r="X56" s="1"/>
-      <c r="Z56" s="57" t="s">
+      <c r="Z56" t="s">
         <v>62</v>
       </c>
-      <c r="AA56" s="57">
+      <c r="AA56">
         <v>6.580415039636632E-2</v>
       </c>
-      <c r="AB56" s="57">
+      <c r="AB56">
         <v>0.23766206774961443</v>
       </c>
-      <c r="AC56" s="57">
+      <c r="AC56">
         <v>0.27688116584802824</v>
       </c>
-      <c r="AD56" s="57">
+      <c r="AD56">
         <v>0.78986904654876833</v>
       </c>
-      <c r="AE56" s="57">
+      <c r="AE56">
         <v>-0.49617733868805947</v>
       </c>
-      <c r="AF56" s="57">
+      <c r="AF56">
         <v>0.62778563948079213</v>
       </c>
-      <c r="AG56" s="57">
+      <c r="AG56">
         <v>-0.49617733868805947</v>
       </c>
-      <c r="AH56" s="57">
+      <c r="AH56">
         <v>0.62778563948079213</v>
       </c>
-      <c r="AJ56" s="57" t="s">
+      <c r="AJ56" t="s">
         <v>62</v>
       </c>
-      <c r="AK56" s="57">
+      <c r="AK56">
         <v>-1.9465861189405778</v>
       </c>
-      <c r="AL56" s="57">
+      <c r="AL56">
         <v>1.5582125458917644</v>
       </c>
-      <c r="AM56" s="57">
+      <c r="AM56">
         <v>-1.2492430022289081</v>
       </c>
-      <c r="AN56" s="57">
+      <c r="AN56">
         <v>0.25172836642194146</v>
       </c>
-      <c r="AO56" s="57">
+      <c r="AO56">
         <v>-5.6311732940923793</v>
       </c>
-      <c r="AP56" s="57">
+      <c r="AP56">
         <v>1.7380010562112238</v>
       </c>
-      <c r="AQ56" s="57">
+      <c r="AQ56">
         <v>-5.6311732940923793</v>
       </c>
-      <c r="AR56" s="57">
+      <c r="AR56">
         <v>1.7380010562112238</v>
       </c>
     </row>
@@ -56059,7 +58044,7 @@
       <c r="A57" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B57" s="62">
+      <c r="B57" s="61">
         <v>0.12</v>
       </c>
       <c r="C57" s="17">
@@ -56069,7 +58054,7 @@
         <v>125.17995179</v>
       </c>
       <c r="E57" s="18">
-        <f>D57/C57</f>
+        <f t="shared" si="8"/>
         <v>1.0396485920727681</v>
       </c>
       <c r="F57" s="18">
@@ -56082,67 +58067,67 @@
         <v>2</v>
       </c>
       <c r="I57" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-0.75</v>
       </c>
-      <c r="J57" s="69">
+      <c r="J57" s="15">
         <v>-4.3</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="1"/>
       <c r="X57" s="1"/>
-      <c r="Z57" s="58" t="s">
+      <c r="Z57" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="AA57" s="58">
+      <c r="AA57" s="57">
         <v>7.4439463962504213E-3</v>
       </c>
-      <c r="AB57" s="58">
+      <c r="AB57" s="57">
         <v>6.516010779922218E-3</v>
       </c>
-      <c r="AC57" s="58">
+      <c r="AC57" s="57">
         <v>1.1424085453000554</v>
       </c>
-      <c r="AD57" s="58">
+      <c r="AD57" s="57">
         <v>0.29084943877917607</v>
       </c>
-      <c r="AE57" s="58">
+      <c r="AE57" s="57">
         <v>-7.9639707175936728E-3</v>
       </c>
-      <c r="AF57" s="58">
+      <c r="AF57" s="57">
         <v>2.2851863510094515E-2</v>
       </c>
-      <c r="AG57" s="58">
+      <c r="AG57" s="57">
         <v>-7.9639707175936728E-3</v>
       </c>
-      <c r="AH57" s="58">
+      <c r="AH57" s="57">
         <v>2.2851863510094515E-2</v>
       </c>
-      <c r="AJ57" s="58" t="s">
+      <c r="AJ57" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="AK57" s="58">
+      <c r="AK57" s="57">
         <v>-1.6024930431275432E-3</v>
       </c>
-      <c r="AL57" s="58">
+      <c r="AL57" s="57">
         <v>4.2721709200719743E-2</v>
       </c>
-      <c r="AM57" s="58">
+      <c r="AM57" s="57">
         <v>-3.7510040518241847E-2</v>
       </c>
-      <c r="AN57" s="58">
+      <c r="AN57" s="57">
         <v>0.97112564824448833</v>
       </c>
-      <c r="AO57" s="58">
+      <c r="AO57" s="57">
         <v>-0.10262328268864405</v>
       </c>
-      <c r="AP57" s="58">
+      <c r="AP57" s="57">
         <v>9.9418296602388975E-2</v>
       </c>
-      <c r="AQ57" s="58">
+      <c r="AQ57" s="57">
         <v>-0.10262328268864405</v>
       </c>
-      <c r="AR57" s="58">
+      <c r="AR57" s="57">
         <v>9.9418296602388975E-2</v>
       </c>
     </row>
@@ -56160,7 +58145,7 @@
         <v>128.631154973333</v>
       </c>
       <c r="E58" s="18">
-        <f>D58/C58</f>
+        <f t="shared" si="8"/>
         <v>1.0831630031367767</v>
       </c>
       <c r="F58" s="18">
@@ -56173,10 +58158,10 @@
         <v>7.25</v>
       </c>
       <c r="I58" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-3.5</v>
       </c>
-      <c r="J58" s="69">
+      <c r="J58" s="15">
         <v>-8.3000000000000007</v>
       </c>
       <c r="K58" s="1"/>
@@ -56208,7 +58193,7 @@
         <v>127.417386873333</v>
       </c>
       <c r="E59" s="18">
-        <f>D59/C59</f>
+        <f t="shared" si="8"/>
         <v>1.0183454205725238</v>
       </c>
       <c r="F59" s="18">
@@ -56221,10 +58206,10 @@
         <v>4.75</v>
       </c>
       <c r="I59" s="15">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>-4.25</v>
       </c>
-      <c r="J59" s="69">
+      <c r="J59" s="15">
         <v>-9.8000000000000007</v>
       </c>
     </row>
@@ -56313,7 +58298,7 @@
       <c r="G64" s="15"/>
       <c r="H64" s="15"/>
       <c r="I64" s="15"/>
-      <c r="J64" s="67"/>
+      <c r="J64" s="18"/>
       <c r="L64" s="15" t="s">
         <v>14</v>
       </c>
@@ -56359,10 +58344,10 @@
         <v>0</v>
       </c>
       <c r="I65" s="15">
-        <f t="shared" ref="I65:I67" si="5">G65-H65</f>
+        <f t="shared" ref="I65:I67" si="10">G65-H65</f>
         <v>0.25</v>
       </c>
-      <c r="J65" s="68">
+      <c r="J65" s="19">
         <v>-1.2333333333333301</v>
       </c>
       <c r="L65" s="15" t="s">
@@ -56410,10 +58395,10 @@
         <v>3.5</v>
       </c>
       <c r="I66" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>-3.25</v>
       </c>
-      <c r="J66" s="68">
+      <c r="J66" s="19">
         <v>-0.233333333333333</v>
       </c>
       <c r="L66" s="15" t="s">
@@ -56461,10 +58446,10 @@
         <v>0</v>
       </c>
       <c r="I67" s="15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="J67" s="68">
+      <c r="J67" s="19">
         <v>0</v>
       </c>
       <c r="L67" s="15" t="s">
@@ -56502,7 +58487,7 @@
       <c r="G68" s="15"/>
       <c r="H68" s="15"/>
       <c r="I68" s="15"/>
-      <c r="J68" s="68"/>
+      <c r="J68" s="19"/>
       <c r="L68" s="15" t="s">
         <v>25</v>
       </c>
@@ -56538,7 +58523,7 @@
       <c r="G69" s="15"/>
       <c r="H69" s="15"/>
       <c r="I69" s="15"/>
-      <c r="J69" s="68"/>
+      <c r="J69" s="19"/>
       <c r="L69" s="15" t="s">
         <v>26</v>
       </c>
@@ -56574,7 +58559,7 @@
       <c r="G70" s="15"/>
       <c r="H70" s="15"/>
       <c r="I70" s="15"/>
-      <c r="J70" s="68"/>
+      <c r="J70" s="19"/>
       <c r="L70" s="15" t="s">
         <v>27</v>
       </c>
@@ -56610,7 +58595,7 @@
       <c r="G71" s="15"/>
       <c r="H71" s="15"/>
       <c r="I71" s="15"/>
-      <c r="J71" s="68"/>
+      <c r="J71" s="19"/>
       <c r="L71" s="15" t="s">
         <v>28</v>
       </c>
@@ -56656,10 +58641,10 @@
         <v>1.25</v>
       </c>
       <c r="I72" s="15">
-        <f t="shared" ref="I72" si="6">G72-H72</f>
+        <f t="shared" ref="I72" si="11">G72-H72</f>
         <v>-0.75</v>
       </c>
-      <c r="J72" s="69">
+      <c r="J72" s="15">
         <v>-3.05</v>
       </c>
       <c r="L72" s="15" t="s">
@@ -56697,7 +58682,7 @@
       <c r="G73" s="15"/>
       <c r="H73" s="15"/>
       <c r="I73" s="15"/>
-      <c r="J73" s="68"/>
+      <c r="J73" s="19"/>
       <c r="L73" s="15" t="s">
         <v>30</v>
       </c>
@@ -56743,10 +58728,10 @@
         <v>1.5</v>
       </c>
       <c r="I74" s="15">
-        <f t="shared" ref="I74:I79" si="7">G74-H74</f>
+        <f t="shared" ref="I74:I79" si="12">G74-H74</f>
         <v>-1</v>
       </c>
-      <c r="J74" s="69">
+      <c r="J74" s="15">
         <v>-5.3</v>
       </c>
     </row>
@@ -56776,10 +58761,10 @@
         <v>1.25</v>
       </c>
       <c r="I75" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-1.25</v>
       </c>
-      <c r="J75" s="69">
+      <c r="J75" s="15">
         <v>11.95</v>
       </c>
     </row>
@@ -56809,10 +58794,10 @@
         <v>4.75</v>
       </c>
       <c r="I76" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-3.5</v>
       </c>
-      <c r="J76" s="69">
+      <c r="J76" s="15">
         <v>-6.3</v>
       </c>
       <c r="L76" t="s">
@@ -56854,29 +58839,29 @@
         <v>2</v>
       </c>
       <c r="I77" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-0.75</v>
       </c>
-      <c r="J77" s="69">
+      <c r="J77" s="15">
         <v>-4.3</v>
       </c>
-      <c r="L77" s="60" t="s">
+      <c r="L77" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="M77" s="60"/>
-      <c r="V77" s="60" t="s">
+      <c r="M77" s="59"/>
+      <c r="V77" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="W77" s="60"/>
-      <c r="X77" s="60"/>
-      <c r="AG77" s="60" t="s">
+      <c r="W77" s="59"/>
+      <c r="X77" s="59"/>
+      <c r="AG77" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AH77" s="60"/>
-      <c r="AQ77" s="60" t="s">
+      <c r="AH77" s="59"/>
+      <c r="AQ77" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AR77" s="60"/>
+      <c r="AR77" s="59"/>
     </row>
     <row r="78" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A78" s="15" t="s">
@@ -56904,35 +58889,34 @@
         <v>7.25</v>
       </c>
       <c r="I78" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-3.5</v>
       </c>
-      <c r="J78" s="69">
+      <c r="J78" s="15">
         <v>-8.3000000000000007</v>
       </c>
-      <c r="L78" s="57" t="s">
+      <c r="L78" t="s">
         <v>38</v>
       </c>
-      <c r="M78" s="57">
+      <c r="M78">
         <v>0.50659377898911795</v>
       </c>
-      <c r="V78" s="57" t="s">
+      <c r="V78" t="s">
         <v>38</v>
       </c>
-      <c r="W78" s="57"/>
-      <c r="X78" s="57">
+      <c r="X78">
         <v>0.23076236633326122</v>
       </c>
-      <c r="AG78" s="57" t="s">
+      <c r="AG78" t="s">
         <v>38</v>
       </c>
-      <c r="AH78" s="57">
+      <c r="AH78">
         <v>0.42743669497884135</v>
       </c>
-      <c r="AQ78" s="57" t="s">
+      <c r="AQ78" t="s">
         <v>38</v>
       </c>
-      <c r="AR78" s="57">
+      <c r="AR78">
         <v>0.12727689883679735</v>
       </c>
     </row>
@@ -56962,89 +58946,86 @@
         <v>4.75</v>
       </c>
       <c r="I79" s="15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="12"/>
         <v>-4.25</v>
       </c>
-      <c r="J79" s="69">
+      <c r="J79" s="15">
         <v>-9.8000000000000007</v>
       </c>
-      <c r="L79" s="57" t="s">
+      <c r="L79" t="s">
         <v>39</v>
       </c>
-      <c r="M79" s="57">
+      <c r="M79">
         <v>0.25663725691047523</v>
       </c>
-      <c r="V79" s="57" t="s">
+      <c r="V79" t="s">
         <v>39</v>
       </c>
-      <c r="W79" s="57"/>
-      <c r="X79" s="57">
+      <c r="X79">
         <v>5.3251269715726246E-2</v>
       </c>
-      <c r="AG79" s="57" t="s">
+      <c r="AG79" t="s">
         <v>39</v>
       </c>
-      <c r="AH79" s="57">
+      <c r="AH79">
         <v>0.18270212821443504</v>
       </c>
-      <c r="AQ79" s="57" t="s">
+      <c r="AQ79" t="s">
         <v>39</v>
       </c>
-      <c r="AR79" s="57">
+      <c r="AR79">
         <v>1.6199408977512351E-2</v>
       </c>
     </row>
     <row r="80" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="L80" s="57" t="s">
+      <c r="L80" t="s">
         <v>40</v>
       </c>
-      <c r="M80" s="57">
+      <c r="M80">
         <v>0.16371691402428462</v>
       </c>
-      <c r="V80" s="57" t="s">
+      <c r="V80" t="s">
         <v>40</v>
       </c>
-      <c r="W80" s="57"/>
-      <c r="X80" s="57">
+      <c r="X80">
         <v>-6.5092321569807973E-2</v>
       </c>
-      <c r="AG80" s="57" t="s">
+      <c r="AG80" t="s">
         <v>40</v>
       </c>
-      <c r="AH80" s="57">
+      <c r="AH80">
         <v>8.0539894241239418E-2</v>
       </c>
-      <c r="AQ80" s="57" t="s">
+      <c r="AQ80" t="s">
         <v>40</v>
       </c>
-      <c r="AR80" s="57">
+      <c r="AR80">
         <v>-0.10677566490029861</v>
       </c>
     </row>
     <row r="81" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="L81" s="57" t="s">
+      <c r="L81" t="s">
         <v>41</v>
       </c>
-      <c r="M81" s="57">
+      <c r="M81">
         <v>7.2605125270895507E-2</v>
       </c>
-      <c r="V81" s="57" t="s">
+      <c r="V81" t="s">
         <v>41</v>
       </c>
-      <c r="W81" s="57"/>
-      <c r="X81" s="57">
+      <c r="X81">
         <v>0.18440153153628142</v>
       </c>
-      <c r="AG81" s="57" t="s">
+      <c r="AG81" t="s">
         <v>41</v>
       </c>
-      <c r="AH81" s="57">
+      <c r="AH81">
         <v>3.2221420462460897E-2</v>
       </c>
-      <c r="AQ81" s="57" t="s">
+      <c r="AQ81" t="s">
         <v>41</v>
       </c>
-      <c r="AR81" s="57">
+      <c r="AR81">
         <v>0.23235367835555554</v>
       </c>
     </row>
@@ -57054,29 +59035,29 @@
       </c>
       <c r="B82" s="10"/>
       <c r="C82" s="10"/>
-      <c r="L82" s="58" t="s">
+      <c r="L82" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="M82" s="58">
+      <c r="M82" s="57">
         <v>10</v>
       </c>
-      <c r="V82" s="58" t="s">
+      <c r="V82" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="W82" s="58"/>
-      <c r="X82" s="58">
+      <c r="W82" s="57"/>
+      <c r="X82" s="57">
         <v>10</v>
       </c>
-      <c r="AG82" s="58" t="s">
+      <c r="AG82" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AH82" s="58">
+      <c r="AH82" s="57">
         <v>10</v>
       </c>
-      <c r="AQ82" s="58" t="s">
+      <c r="AQ82" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AR82" s="58">
+      <c r="AR82" s="57">
         <v>10</v>
       </c>
     </row>
@@ -57122,69 +59103,69 @@
       <c r="C85" s="17">
         <v>60.588347259999999</v>
       </c>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59" t="s">
+      <c r="L85" s="58"/>
+      <c r="M85" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="N85" s="59" t="s">
+      <c r="N85" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="O85" s="59" t="s">
+      <c r="O85" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="P85" s="59" t="s">
+      <c r="P85" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="Q85" s="59" t="s">
+      <c r="Q85" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="V85" s="59"/>
-      <c r="W85" s="59"/>
-      <c r="X85" s="59" t="s">
+      <c r="V85" s="58"/>
+      <c r="W85" s="58"/>
+      <c r="X85" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="Y85" s="59" t="s">
+      <c r="Y85" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="Z85" s="59" t="s">
+      <c r="Z85" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AA85" s="59" t="s">
+      <c r="AA85" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AB85" s="59" t="s">
+      <c r="AB85" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AG85" s="59"/>
-      <c r="AH85" s="59" t="s">
+      <c r="AG85" s="58"/>
+      <c r="AH85" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AI85" s="59" t="s">
+      <c r="AI85" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AJ85" s="59" t="s">
+      <c r="AJ85" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AK85" s="59" t="s">
+      <c r="AK85" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AL85" s="59" t="s">
+      <c r="AL85" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AQ85" s="59"/>
-      <c r="AR85" s="59" t="s">
+      <c r="AQ85" s="58"/>
+      <c r="AR85" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AS85" s="59" t="s">
+      <c r="AS85" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AT85" s="59" t="s">
+      <c r="AT85" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AU85" s="59" t="s">
+      <c r="AU85" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AV85" s="59" t="s">
+      <c r="AV85" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -57198,77 +59179,76 @@
       <c r="C86" s="17">
         <v>73.387016439999996</v>
       </c>
-      <c r="L86" s="57" t="s">
+      <c r="L86" t="s">
         <v>44</v>
       </c>
-      <c r="M86" s="57">
+      <c r="M86">
         <v>1</v>
       </c>
-      <c r="N86" s="57">
+      <c r="N86">
         <v>1.4559399370073466E-2</v>
       </c>
-      <c r="O86" s="57">
+      <c r="O86">
         <v>1.4559399370073466E-2</v>
       </c>
-      <c r="P86" s="57">
+      <c r="P86">
         <v>2.7619060470408092</v>
       </c>
-      <c r="Q86" s="57">
+      <c r="Q86">
         <v>0.13510832814324739</v>
       </c>
-      <c r="V86" s="57" t="s">
+      <c r="V86" t="s">
         <v>44</v>
       </c>
-      <c r="W86" s="57"/>
-      <c r="X86" s="57">
+      <c r="X86">
         <v>1</v>
       </c>
-      <c r="Y86" s="57">
+      <c r="Y86">
         <v>1.5300804657030653E-2</v>
       </c>
-      <c r="Z86" s="57">
+      <c r="Z86">
         <v>1.5300804657030653E-2</v>
       </c>
-      <c r="AA86" s="57">
+      <c r="AA86">
         <v>0.44997172332926694</v>
       </c>
-      <c r="AB86" s="57">
+      <c r="AB86">
         <v>0.52124020036226892</v>
       </c>
-      <c r="AG86" s="57" t="s">
+      <c r="AG86" t="s">
         <v>44</v>
       </c>
-      <c r="AH86" s="57">
+      <c r="AH86">
         <v>1</v>
       </c>
-      <c r="AI86" s="57">
+      <c r="AI86">
         <v>1.8567036428026717E-3</v>
       </c>
-      <c r="AJ86" s="57">
+      <c r="AJ86">
         <v>1.8567036428026717E-3</v>
       </c>
-      <c r="AK86" s="57">
+      <c r="AK86">
         <v>1.7883529080067957</v>
       </c>
-      <c r="AL86" s="57">
+      <c r="AL86">
         <v>0.21790000787407429</v>
       </c>
-      <c r="AQ86" s="57" t="s">
+      <c r="AQ86" t="s">
         <v>44</v>
       </c>
-      <c r="AR86" s="57">
+      <c r="AR86">
         <v>1</v>
       </c>
-      <c r="AS86" s="57">
+      <c r="AS86">
         <v>7.1118269748280949E-3</v>
       </c>
-      <c r="AT86" s="57">
+      <c r="AT86">
         <v>7.1118269748280949E-3</v>
       </c>
-      <c r="AU86" s="57">
+      <c r="AU86">
         <v>0.13172920712052766</v>
       </c>
-      <c r="AV86" s="57">
+      <c r="AV86">
         <v>0.72604832578033163</v>
       </c>
     </row>
@@ -57282,63 +59262,54 @@
       <c r="C87" s="17">
         <v>79.767295559999994</v>
       </c>
-      <c r="L87" s="57" t="s">
+      <c r="L87" t="s">
         <v>45</v>
       </c>
-      <c r="M87" s="57">
+      <c r="M87">
         <v>8</v>
       </c>
-      <c r="N87" s="57">
+      <c r="N87">
         <v>4.2172033724819431E-2</v>
       </c>
-      <c r="O87" s="57">
+      <c r="O87">
         <v>5.2715042156024289E-3</v>
       </c>
-      <c r="P87" s="57"/>
-      <c r="Q87" s="57"/>
-      <c r="V87" s="57" t="s">
+      <c r="V87" t="s">
         <v>45</v>
       </c>
-      <c r="W87" s="57"/>
-      <c r="X87" s="57">
+      <c r="X87">
         <v>8</v>
       </c>
-      <c r="Y87" s="57">
+      <c r="Y87">
         <v>0.27203139866340953</v>
       </c>
-      <c r="Z87" s="57">
+      <c r="Z87">
         <v>3.4003924832926191E-2</v>
       </c>
-      <c r="AA87" s="57"/>
-      <c r="AB87" s="57"/>
-      <c r="AG87" s="57" t="s">
+      <c r="AG87" t="s">
         <v>45</v>
       </c>
-      <c r="AH87" s="57">
+      <c r="AH87">
         <v>8</v>
       </c>
-      <c r="AI87" s="57">
+      <c r="AI87">
         <v>8.3057594929495486E-3</v>
       </c>
-      <c r="AJ87" s="57">
+      <c r="AJ87">
         <v>1.0382199366186936E-3</v>
       </c>
-      <c r="AK87" s="57"/>
-      <c r="AL87" s="57"/>
-      <c r="AQ87" s="57" t="s">
+      <c r="AQ87" t="s">
         <v>45</v>
       </c>
-      <c r="AR87" s="57">
+      <c r="AR87">
         <v>8</v>
       </c>
-      <c r="AS87" s="57">
+      <c r="AS87">
         <v>0.4319058547628557</v>
       </c>
-      <c r="AT87" s="57">
+      <c r="AT87">
         <v>5.3988231845356963E-2</v>
       </c>
-      <c r="AU87" s="57"/>
-      <c r="AV87" s="57"/>
     </row>
     <row r="88" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
@@ -57348,55 +59319,55 @@
         <v>4.3375577562074601E-2</v>
       </c>
       <c r="C88" s="17"/>
-      <c r="L88" s="58" t="s">
+      <c r="L88" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="M88" s="58">
+      <c r="M88" s="57">
         <v>9</v>
       </c>
-      <c r="N88" s="58">
+      <c r="N88" s="57">
         <v>5.6731433094892897E-2</v>
       </c>
-      <c r="O88" s="58"/>
-      <c r="P88" s="58"/>
-      <c r="Q88" s="58"/>
-      <c r="V88" s="58" t="s">
+      <c r="O88" s="57"/>
+      <c r="P88" s="57"/>
+      <c r="Q88" s="57"/>
+      <c r="V88" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="W88" s="58"/>
-      <c r="X88" s="58">
+      <c r="W88" s="57"/>
+      <c r="X88" s="57">
         <v>9</v>
       </c>
-      <c r="Y88" s="58">
+      <c r="Y88" s="57">
         <v>0.28733220332044018</v>
       </c>
-      <c r="Z88" s="58"/>
-      <c r="AA88" s="58"/>
-      <c r="AB88" s="58"/>
-      <c r="AG88" s="58" t="s">
+      <c r="Z88" s="57"/>
+      <c r="AA88" s="57"/>
+      <c r="AB88" s="57"/>
+      <c r="AG88" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AH88" s="58">
+      <c r="AH88" s="57">
         <v>9</v>
       </c>
-      <c r="AI88" s="58">
+      <c r="AI88" s="57">
         <v>1.016246313575222E-2</v>
       </c>
-      <c r="AJ88" s="58"/>
-      <c r="AK88" s="58"/>
-      <c r="AL88" s="58"/>
-      <c r="AQ88" s="58" t="s">
+      <c r="AJ88" s="57"/>
+      <c r="AK88" s="57"/>
+      <c r="AL88" s="57"/>
+      <c r="AQ88" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AR88" s="58">
+      <c r="AR88" s="57">
         <v>9</v>
       </c>
-      <c r="AS88" s="58">
+      <c r="AS88" s="57">
         <v>0.4390176817376838</v>
       </c>
-      <c r="AT88" s="58"/>
-      <c r="AU88" s="58"/>
-      <c r="AV88" s="58"/>
+      <c r="AT88" s="57"/>
+      <c r="AU88" s="57"/>
+      <c r="AV88" s="57"/>
     </row>
     <row r="89" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
@@ -57413,105 +59384,105 @@
         <v>-6.6277814143714905E-2</v>
       </c>
       <c r="C90" s="8"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59" t="s">
+      <c r="L90" s="58"/>
+      <c r="M90" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="N90" s="59" t="s">
+      <c r="N90" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="O90" s="59" t="s">
+      <c r="O90" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="P90" s="59" t="s">
+      <c r="P90" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="Q90" s="59" t="s">
+      <c r="Q90" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="R90" s="59" t="s">
+      <c r="R90" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="S90" s="59" t="s">
+      <c r="S90" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="T90" s="59" t="s">
+      <c r="T90" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="V90" s="59"/>
-      <c r="W90" s="59"/>
-      <c r="X90" s="59" t="s">
+      <c r="V90" s="58"/>
+      <c r="W90" s="58"/>
+      <c r="X90" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="Y90" s="59" t="s">
+      <c r="Y90" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="Z90" s="59" t="s">
+      <c r="Z90" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AA90" s="59" t="s">
+      <c r="AA90" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AB90" s="59" t="s">
+      <c r="AB90" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AC90" s="59" t="s">
+      <c r="AC90" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AD90" s="59" t="s">
+      <c r="AD90" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AE90" s="59" t="s">
+      <c r="AE90" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AG90" s="59"/>
-      <c r="AH90" s="59" t="s">
+      <c r="AG90" s="58"/>
+      <c r="AH90" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AI90" s="59" t="s">
+      <c r="AI90" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AJ90" s="59" t="s">
+      <c r="AJ90" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AK90" s="59" t="s">
+      <c r="AK90" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AL90" s="59" t="s">
+      <c r="AL90" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AM90" s="59" t="s">
+      <c r="AM90" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AN90" s="59" t="s">
+      <c r="AN90" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AO90" s="59" t="s">
+      <c r="AO90" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AQ90" s="59"/>
-      <c r="AR90" s="59" t="s">
+      <c r="AQ90" s="58"/>
+      <c r="AR90" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AS90" s="59" t="s">
+      <c r="AS90" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AT90" s="59" t="s">
+      <c r="AT90" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AU90" s="59" t="s">
+      <c r="AU90" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AV90" s="59" t="s">
+      <c r="AV90" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AW90" s="59" t="s">
+      <c r="AW90" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AX90" s="59" t="s">
+      <c r="AX90" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AY90" s="59" t="s">
+      <c r="AY90" s="58" t="s">
         <v>58</v>
       </c>
     </row>
@@ -57519,113 +59490,112 @@
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
       <c r="C91" s="8"/>
-      <c r="L91" s="57" t="s">
+      <c r="L91" t="s">
         <v>47</v>
       </c>
-      <c r="M91" s="57">
+      <c r="M91">
         <v>0.10775041704806361</v>
       </c>
-      <c r="N91" s="57">
+      <c r="N91">
         <v>3.1799159059717086E-2</v>
       </c>
-      <c r="O91" s="57">
+      <c r="O91">
         <v>3.3884675014743064</v>
       </c>
-      <c r="P91" s="57">
+      <c r="P91">
         <v>9.5215315548850786E-3</v>
       </c>
-      <c r="Q91" s="57">
+      <c r="Q91">
         <v>3.4421424760340949E-2</v>
       </c>
-      <c r="R91" s="57">
+      <c r="R91">
         <v>0.18107940933578626</v>
       </c>
-      <c r="S91" s="57">
+      <c r="S91">
         <v>3.4421424760340949E-2</v>
       </c>
-      <c r="T91" s="57">
+      <c r="T91">
         <v>0.18107940933578626</v>
       </c>
-      <c r="V91" s="57" t="s">
+      <c r="V91" t="s">
         <v>47</v>
       </c>
-      <c r="W91" s="57"/>
-      <c r="X91" s="57">
+      <c r="X91">
         <v>-2.8260574150480076E-2</v>
       </c>
-      <c r="Y91" s="57">
+      <c r="Y91">
         <v>8.0763081260438491E-2</v>
       </c>
-      <c r="Z91" s="57">
+      <c r="Z91">
         <v>-0.34991946455519174</v>
       </c>
-      <c r="AA91" s="57">
+      <c r="AA91">
         <v>0.73543280524645183</v>
       </c>
-      <c r="AB91" s="57">
+      <c r="AB91">
         <v>-0.21450057350888141</v>
       </c>
-      <c r="AC91" s="57">
+      <c r="AC91">
         <v>0.15797942520792124</v>
       </c>
-      <c r="AD91" s="57">
+      <c r="AD91">
         <v>-0.21450057350888141</v>
       </c>
-      <c r="AE91" s="57">
+      <c r="AE91">
         <v>0.15797942520792124</v>
       </c>
-      <c r="AG91" s="57" t="s">
+      <c r="AG91" t="s">
         <v>47</v>
       </c>
-      <c r="AH91" s="57">
+      <c r="AH91">
         <v>0.11898501211487846</v>
       </c>
-      <c r="AI91" s="57">
+      <c r="AI91">
         <v>1.411214525962045E-2</v>
       </c>
-      <c r="AJ91" s="57">
+      <c r="AJ91">
         <v>8.431390828673953</v>
       </c>
-      <c r="AK91" s="57">
+      <c r="AK91">
         <v>2.9863699402098115E-5</v>
       </c>
-      <c r="AL91" s="57">
+      <c r="AL91">
         <v>8.6442346789591812E-2</v>
       </c>
-      <c r="AM91" s="57">
+      <c r="AM91">
         <v>0.1515276774401651</v>
       </c>
-      <c r="AN91" s="57">
+      <c r="AN91">
         <v>8.6442346789591812E-2</v>
       </c>
-      <c r="AO91" s="57">
+      <c r="AO91">
         <v>0.1515276774401651</v>
       </c>
-      <c r="AQ91" s="57" t="s">
+      <c r="AQ91" t="s">
         <v>47</v>
       </c>
-      <c r="AR91" s="57">
+      <c r="AR91">
         <v>-0.15591910902676914</v>
       </c>
-      <c r="AS91" s="57">
+      <c r="AS91">
         <v>0.10176487608238409</v>
       </c>
-      <c r="AT91" s="57">
+      <c r="AT91">
         <v>-1.5321505319826096</v>
       </c>
-      <c r="AU91" s="57">
+      <c r="AU91">
         <v>0.16402260874002078</v>
       </c>
-      <c r="AV91" s="57">
+      <c r="AV91">
         <v>-0.39058933409128649</v>
       </c>
-      <c r="AW91" s="57">
+      <c r="AW91">
         <v>7.8751116037748203E-2</v>
       </c>
-      <c r="AX91" s="57">
+      <c r="AX91">
         <v>-0.39058933409128649</v>
       </c>
-      <c r="AY91" s="57">
+      <c r="AY91">
         <v>7.8751116037748203E-2</v>
       </c>
     </row>
@@ -57633,113 +59603,113 @@
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
       <c r="C92" s="8"/>
-      <c r="L92" s="58" t="s">
+      <c r="L92" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="M92" s="58">
+      <c r="M92" s="57">
         <v>2.215947059996258E-2</v>
       </c>
-      <c r="N92" s="58">
+      <c r="N92" s="57">
         <v>1.3333830505123935E-2</v>
       </c>
-      <c r="O92" s="58">
+      <c r="O92" s="57">
         <v>1.6618983263246911</v>
       </c>
-      <c r="P92" s="58">
+      <c r="P92" s="57">
         <v>0.13510832814324722</v>
       </c>
-      <c r="Q92" s="58">
+      <c r="Q92" s="57">
         <v>-8.5883976829646824E-3</v>
       </c>
-      <c r="R92" s="58">
+      <c r="R92" s="57">
         <v>5.2907338882889843E-2</v>
       </c>
-      <c r="S92" s="58">
+      <c r="S92" s="57">
         <v>-8.5883976829646824E-3</v>
       </c>
-      <c r="T92" s="58">
+      <c r="T92" s="57">
         <v>5.2907338882889843E-2</v>
       </c>
-      <c r="V92" s="58" t="s">
+      <c r="V92" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="W92" s="58"/>
-      <c r="X92" s="58">
+      <c r="W92" s="57"/>
+      <c r="X92" s="57">
         <v>2.2716676134609717E-2</v>
       </c>
-      <c r="Y92" s="58">
+      <c r="Y92" s="57">
         <v>3.3865085380903118E-2</v>
       </c>
-      <c r="Z92" s="58">
+      <c r="Z92" s="57">
         <v>0.6707993167328582</v>
       </c>
-      <c r="AA92" s="58">
+      <c r="AA92" s="57">
         <v>0.52124020036226781</v>
       </c>
-      <c r="AB92" s="58">
+      <c r="AB92" s="57">
         <v>-5.5376350792795057E-2</v>
       </c>
-      <c r="AC92" s="58">
+      <c r="AC92" s="57">
         <v>0.10080970306201449</v>
       </c>
-      <c r="AD92" s="58">
+      <c r="AD92" s="57">
         <v>-5.5376350792795057E-2</v>
       </c>
-      <c r="AE92" s="58">
+      <c r="AE92" s="57">
         <v>0.10080970306201449</v>
       </c>
-      <c r="AG92" s="58" t="s">
+      <c r="AG92" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AH92" s="58">
+      <c r="AH92" s="57">
         <v>7.9133239675841498E-3</v>
       </c>
-      <c r="AI92" s="58">
+      <c r="AI92" s="57">
         <v>5.917419155710887E-3</v>
       </c>
-      <c r="AJ92" s="58">
+      <c r="AJ92" s="57">
         <v>1.3372931271814705</v>
       </c>
-      <c r="AK92" s="58">
+      <c r="AK92" s="57">
         <v>0.21790000787407415</v>
       </c>
-      <c r="AL92" s="58">
+      <c r="AL92" s="57">
         <v>-5.7322690752215077E-3</v>
       </c>
-      <c r="AM92" s="58">
+      <c r="AM92" s="57">
         <v>2.1558917010389807E-2</v>
       </c>
-      <c r="AN92" s="58">
+      <c r="AN92" s="57">
         <v>-5.7322690752215077E-3</v>
       </c>
-      <c r="AO92" s="58">
+      <c r="AO92" s="57">
         <v>2.1558917010389807E-2</v>
       </c>
-      <c r="AQ92" s="58" t="s">
+      <c r="AQ92" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AR92" s="58">
+      <c r="AR92" s="57">
         <v>-1.5487390263086643E-2</v>
       </c>
-      <c r="AS92" s="58">
+      <c r="AS92" s="57">
         <v>4.2671430603219304E-2</v>
       </c>
-      <c r="AT92" s="58">
+      <c r="AT92" s="57">
         <v>-0.36294518473252713</v>
       </c>
-      <c r="AU92" s="58">
+      <c r="AU92" s="57">
         <v>0.72604832578033107</v>
       </c>
-      <c r="AV92" s="58">
+      <c r="AV92" s="57">
         <v>-0.11388788568918801</v>
       </c>
-      <c r="AW92" s="58">
+      <c r="AW92" s="57">
         <v>8.2913105163014728E-2</v>
       </c>
-      <c r="AX92" s="58">
+      <c r="AX92" s="57">
         <v>-0.11388788568918801</v>
       </c>
-      <c r="AY92" s="58">
+      <c r="AY92" s="57">
         <v>8.2913105163014728E-2</v>
       </c>
     </row>
@@ -57763,156 +59733,152 @@
       </c>
     </row>
     <row r="95" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="L95" s="60" t="s">
+      <c r="L95" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="M95" s="60"/>
-      <c r="V95" s="60" t="s">
+      <c r="M95" s="59"/>
+      <c r="V95" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="W95" s="60"/>
-      <c r="X95" s="60"/>
-      <c r="AG95" s="60" t="s">
+      <c r="W95" s="59"/>
+      <c r="X95" s="59"/>
+      <c r="AG95" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AH95" s="60"/>
-      <c r="AQ95" s="60" t="s">
+      <c r="AH95" s="59"/>
+      <c r="AQ95" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AR95" s="60"/>
+      <c r="AR95" s="59"/>
     </row>
     <row r="96" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="L96" s="57" t="s">
+      <c r="L96" t="s">
         <v>38</v>
       </c>
-      <c r="M96" s="57">
+      <c r="M96">
         <v>0.9185026256430604</v>
       </c>
-      <c r="V96" s="57" t="s">
+      <c r="V96" t="s">
         <v>38</v>
       </c>
-      <c r="W96" s="57"/>
-      <c r="X96" s="57">
+      <c r="X96">
         <v>0.95970687470483784</v>
       </c>
-      <c r="AG96" s="57" t="s">
+      <c r="AG96" t="s">
         <v>38</v>
       </c>
-      <c r="AH96" s="57">
+      <c r="AH96">
         <v>0.944059556923732</v>
       </c>
-      <c r="AQ96" s="57" t="s">
+      <c r="AQ96" t="s">
         <v>38</v>
       </c>
-      <c r="AR96" s="57">
+      <c r="AR96">
         <v>0.36712737728751571</v>
       </c>
     </row>
     <row r="97" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L97" s="57" t="s">
+      <c r="L97" t="s">
         <v>39</v>
       </c>
-      <c r="M97" s="57">
+      <c r="M97">
         <v>0.84364707331319588</v>
       </c>
-      <c r="V97" s="57" t="s">
+      <c r="V97" t="s">
         <v>39</v>
       </c>
-      <c r="W97" s="57"/>
-      <c r="X97" s="57">
+      <c r="X97">
         <v>0.92103728535572738</v>
       </c>
-      <c r="AG97" s="57" t="s">
+      <c r="AG97" t="s">
         <v>39</v>
       </c>
-      <c r="AH97" s="57">
+      <c r="AH97">
         <v>0.89124844701903316</v>
       </c>
-      <c r="AQ97" s="57" t="s">
+      <c r="AQ97" t="s">
         <v>39</v>
       </c>
-      <c r="AR97" s="57">
+      <c r="AR97">
         <v>0.13478251115400991</v>
       </c>
     </row>
     <row r="98" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L98" s="57" t="s">
+      <c r="L98" t="s">
         <v>40</v>
       </c>
-      <c r="M98" s="57">
+      <c r="M98">
         <v>0.68729414662639177</v>
       </c>
-      <c r="V98" s="57" t="s">
+      <c r="V98" t="s">
         <v>40</v>
       </c>
-      <c r="W98" s="57"/>
-      <c r="X98" s="57">
+      <c r="X98">
         <v>0.84207457071145475</v>
       </c>
-      <c r="AG98" s="57" t="s">
+      <c r="AG98" t="s">
         <v>40</v>
       </c>
-      <c r="AH98" s="57">
+      <c r="AH98">
         <v>0.78249689403806633</v>
       </c>
-      <c r="AQ98" s="57" t="s">
+      <c r="AQ98" t="s">
         <v>40</v>
       </c>
-      <c r="AR98" s="57">
+      <c r="AR98">
         <v>-0.73043497769198018</v>
       </c>
     </row>
     <row r="99" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L99" s="57" t="s">
+      <c r="L99" t="s">
         <v>41</v>
       </c>
-      <c r="M99" s="57">
+      <c r="M99">
         <v>3.2176802256286052E-2</v>
       </c>
-      <c r="V99" s="57" t="s">
+      <c r="V99" t="s">
         <v>41</v>
       </c>
-      <c r="W99" s="57"/>
-      <c r="X99" s="57">
+      <c r="X99">
         <v>0.11287889738350131</v>
       </c>
-      <c r="AG99" s="57" t="s">
+      <c r="AG99" t="s">
         <v>41</v>
       </c>
-      <c r="AH99" s="57">
+      <c r="AH99">
         <v>1.4329074303957813E-2</v>
       </c>
-      <c r="AQ99" s="57" t="s">
+      <c r="AQ99" t="s">
         <v>41</v>
       </c>
-      <c r="AR99" s="57">
+      <c r="AR99">
         <v>0.23235068371476744</v>
       </c>
     </row>
     <row r="100" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L100" s="58" t="s">
+      <c r="L100" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="M100" s="58">
+      <c r="M100" s="57">
         <v>3</v>
       </c>
-      <c r="V100" s="58" t="s">
+      <c r="V100" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="W100" s="58"/>
-      <c r="X100" s="58">
+      <c r="W100" s="57"/>
+      <c r="X100" s="57">
         <v>3</v>
       </c>
-      <c r="AG100" s="58" t="s">
+      <c r="AG100" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AH100" s="58">
+      <c r="AH100" s="57">
         <v>3</v>
       </c>
-      <c r="AQ100" s="58" t="s">
+      <c r="AQ100" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AR100" s="58">
+      <c r="AR100" s="57">
         <v>3</v>
       </c>
     </row>
@@ -57931,580 +59897,569 @@
       </c>
     </row>
     <row r="103" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L103" s="59"/>
-      <c r="M103" s="59" t="s">
+      <c r="L103" s="58"/>
+      <c r="M103" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="N103" s="59" t="s">
+      <c r="N103" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="O103" s="59" t="s">
+      <c r="O103" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="P103" s="59" t="s">
+      <c r="P103" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="Q103" s="59" t="s">
+      <c r="Q103" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="V103" s="59"/>
-      <c r="W103" s="59"/>
-      <c r="X103" s="59" t="s">
+      <c r="V103" s="58"/>
+      <c r="W103" s="58"/>
+      <c r="X103" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="Y103" s="59" t="s">
+      <c r="Y103" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="Z103" s="59" t="s">
+      <c r="Z103" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AA103" s="59" t="s">
+      <c r="AA103" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AB103" s="59" t="s">
+      <c r="AB103" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AG103" s="59"/>
-      <c r="AH103" s="59" t="s">
+      <c r="AG103" s="58"/>
+      <c r="AH103" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AI103" s="59" t="s">
+      <c r="AI103" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AJ103" s="59" t="s">
+      <c r="AJ103" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AK103" s="59" t="s">
+      <c r="AK103" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AL103" s="59" t="s">
+      <c r="AL103" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AQ103" s="59"/>
-      <c r="AR103" s="59" t="s">
+      <c r="AQ103" s="58"/>
+      <c r="AR103" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AS103" s="59" t="s">
+      <c r="AS103" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AT103" s="59" t="s">
+      <c r="AT103" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AU103" s="59" t="s">
+      <c r="AU103" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AV103" s="59" t="s">
+      <c r="AV103" s="58" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="104" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L104" s="57" t="s">
+      <c r="L104" t="s">
         <v>44</v>
       </c>
-      <c r="M104" s="57">
+      <c r="M104">
         <v>1</v>
       </c>
-      <c r="N104" s="57">
+      <c r="N104">
         <v>5.5865096379468489E-3</v>
       </c>
-      <c r="O104" s="57">
+      <c r="O104">
         <v>5.5865096379468489E-3</v>
       </c>
-      <c r="P104" s="57">
+      <c r="P104">
         <v>5.3957868982083994</v>
       </c>
-      <c r="Q104" s="57">
+      <c r="Q104">
         <v>0.25879835026214731</v>
       </c>
-      <c r="V104" s="57" t="s">
+      <c r="V104" t="s">
         <v>44</v>
       </c>
-      <c r="W104" s="57"/>
-      <c r="X104" s="57">
+      <c r="X104">
         <v>1</v>
       </c>
-      <c r="Y104" s="57">
+      <c r="Y104">
         <v>0.14862116394656652</v>
       </c>
-      <c r="Z104" s="57">
+      <c r="Z104">
         <v>0.14862116394656652</v>
       </c>
-      <c r="AA104" s="57">
+      <c r="AA104">
         <v>11.664204928933909</v>
       </c>
-      <c r="AB104" s="57">
+      <c r="AB104">
         <v>0.18133421153090101</v>
       </c>
-      <c r="AG104" s="57" t="s">
+      <c r="AG104" t="s">
         <v>44</v>
       </c>
-      <c r="AH104" s="57">
+      <c r="AH104">
         <v>1</v>
       </c>
-      <c r="AI104" s="57">
+      <c r="AI104">
         <v>1.6826724653461263E-3</v>
       </c>
-      <c r="AJ104" s="57">
+      <c r="AJ104">
         <v>1.6826724653461263E-3</v>
       </c>
-      <c r="AK104" s="57">
+      <c r="AK104">
         <v>8.195270987762493</v>
       </c>
-      <c r="AL104" s="57">
+      <c r="AL104">
         <v>0.21394577442032442</v>
       </c>
-      <c r="AQ104" s="57" t="s">
+      <c r="AQ104" t="s">
         <v>44</v>
       </c>
-      <c r="AR104" s="57">
+      <c r="AR104">
         <v>1</v>
       </c>
-      <c r="AS104" s="57">
+      <c r="AS104">
         <v>8.4100032515451381E-3</v>
       </c>
-      <c r="AT104" s="57">
+      <c r="AT104">
         <v>8.4100032515451381E-3</v>
       </c>
-      <c r="AU104" s="57">
+      <c r="AU104">
         <v>0.15577876417382658</v>
       </c>
-      <c r="AV104" s="57">
+      <c r="AV104">
         <v>0.76068262316919988</v>
       </c>
     </row>
     <row r="105" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L105" s="57" t="s">
+      <c r="L105" t="s">
         <v>45</v>
       </c>
-      <c r="M105" s="57">
+      <c r="M105">
         <v>1</v>
       </c>
-      <c r="N105" s="57">
+      <c r="N105">
         <v>1.0353466034401352E-3</v>
       </c>
-      <c r="O105" s="57">
+      <c r="O105">
         <v>1.0353466034401352E-3</v>
       </c>
-      <c r="P105" s="57"/>
-      <c r="Q105" s="57"/>
-      <c r="V105" s="57" t="s">
+      <c r="V105" t="s">
         <v>45</v>
       </c>
-      <c r="W105" s="57"/>
-      <c r="X105" s="57">
+      <c r="X105">
         <v>1</v>
       </c>
-      <c r="Y105" s="57">
+      <c r="Y105">
         <v>1.2741645474515019E-2</v>
       </c>
-      <c r="Z105" s="57">
+      <c r="Z105">
         <v>1.2741645474515019E-2</v>
       </c>
-      <c r="AA105" s="57"/>
-      <c r="AB105" s="57"/>
-      <c r="AG105" s="57" t="s">
+      <c r="AG105" t="s">
         <v>45</v>
       </c>
-      <c r="AH105" s="57">
+      <c r="AH105">
         <v>1</v>
       </c>
-      <c r="AI105" s="57">
+      <c r="AI105">
         <v>2.0532237040834408E-4</v>
       </c>
-      <c r="AJ105" s="57">
+      <c r="AJ105">
         <v>2.0532237040834408E-4</v>
       </c>
-      <c r="AK105" s="57"/>
-      <c r="AL105" s="57"/>
-      <c r="AQ105" s="57" t="s">
+      <c r="AQ105" t="s">
         <v>45</v>
       </c>
-      <c r="AR105" s="57">
+      <c r="AR105">
         <v>1</v>
       </c>
-      <c r="AS105" s="57">
+      <c r="AS105">
         <v>5.3986840222719899E-2</v>
       </c>
-      <c r="AT105" s="57">
+      <c r="AT105">
         <v>5.3986840222719899E-2</v>
       </c>
-      <c r="AU105" s="57"/>
-      <c r="AV105" s="57"/>
     </row>
     <row r="106" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L106" s="58" t="s">
+      <c r="L106" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="M106" s="58">
+      <c r="M106" s="57">
         <v>2</v>
       </c>
-      <c r="N106" s="58">
+      <c r="N106" s="57">
         <v>6.6218562413869839E-3</v>
       </c>
-      <c r="O106" s="58"/>
-      <c r="P106" s="58"/>
-      <c r="Q106" s="58"/>
-      <c r="V106" s="58" t="s">
+      <c r="O106" s="57"/>
+      <c r="P106" s="57"/>
+      <c r="Q106" s="57"/>
+      <c r="V106" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="W106" s="58"/>
-      <c r="X106" s="58">
+      <c r="W106" s="57"/>
+      <c r="X106" s="57">
         <v>2</v>
       </c>
-      <c r="Y106" s="58">
+      <c r="Y106" s="57">
         <v>0.16136280942108153</v>
       </c>
-      <c r="Z106" s="58"/>
-      <c r="AA106" s="58"/>
-      <c r="AB106" s="58"/>
-      <c r="AG106" s="58" t="s">
+      <c r="Z106" s="57"/>
+      <c r="AA106" s="57"/>
+      <c r="AB106" s="57"/>
+      <c r="AG106" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AH106" s="58">
+      <c r="AH106" s="57">
         <v>2</v>
       </c>
-      <c r="AI106" s="58">
+      <c r="AI106" s="57">
         <v>1.8879948357544704E-3</v>
       </c>
-      <c r="AJ106" s="58"/>
-      <c r="AK106" s="58"/>
-      <c r="AL106" s="58"/>
-      <c r="AQ106" s="58" t="s">
+      <c r="AJ106" s="57"/>
+      <c r="AK106" s="57"/>
+      <c r="AL106" s="57"/>
+      <c r="AQ106" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AR106" s="58">
+      <c r="AR106" s="57">
         <v>2</v>
       </c>
-      <c r="AS106" s="58">
+      <c r="AS106" s="57">
         <v>6.2396843474265037E-2</v>
       </c>
-      <c r="AT106" s="58"/>
-      <c r="AU106" s="58"/>
-      <c r="AV106" s="58"/>
+      <c r="AT106" s="57"/>
+      <c r="AU106" s="57"/>
+      <c r="AV106" s="57"/>
     </row>
     <row r="107" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L108" s="59"/>
-      <c r="M108" s="59" t="s">
+      <c r="L108" s="58"/>
+      <c r="M108" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="N108" s="59" t="s">
+      <c r="N108" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="O108" s="59" t="s">
+      <c r="O108" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="P108" s="59" t="s">
+      <c r="P108" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="Q108" s="59" t="s">
+      <c r="Q108" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="R108" s="59" t="s">
+      <c r="R108" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="S108" s="59" t="s">
+      <c r="S108" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="T108" s="59" t="s">
+      <c r="T108" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="V108" s="59"/>
-      <c r="W108" s="59"/>
-      <c r="X108" s="59" t="s">
+      <c r="V108" s="58"/>
+      <c r="W108" s="58"/>
+      <c r="X108" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="Y108" s="59" t="s">
+      <c r="Y108" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="Z108" s="59" t="s">
+      <c r="Z108" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AA108" s="59" t="s">
+      <c r="AA108" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AB108" s="59" t="s">
+      <c r="AB108" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AC108" s="59" t="s">
+      <c r="AC108" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AD108" s="59" t="s">
+      <c r="AD108" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AE108" s="59" t="s">
+      <c r="AE108" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AG108" s="59"/>
-      <c r="AH108" s="59" t="s">
+      <c r="AG108" s="58"/>
+      <c r="AH108" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AI108" s="59" t="s">
+      <c r="AI108" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AJ108" s="59" t="s">
+      <c r="AJ108" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AK108" s="59" t="s">
+      <c r="AK108" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AL108" s="59" t="s">
+      <c r="AL108" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AM108" s="59" t="s">
+      <c r="AM108" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AN108" s="59" t="s">
+      <c r="AN108" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AO108" s="59" t="s">
+      <c r="AO108" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AQ108" s="59"/>
-      <c r="AR108" s="59" t="s">
+      <c r="AQ108" s="58"/>
+      <c r="AR108" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AS108" s="59" t="s">
+      <c r="AS108" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AT108" s="59" t="s">
+      <c r="AT108" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AU108" s="59" t="s">
+      <c r="AU108" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AV108" s="59" t="s">
+      <c r="AV108" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AW108" s="59" t="s">
+      <c r="AW108" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AX108" s="59" t="s">
+      <c r="AX108" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AY108" s="59" t="s">
+      <c r="AY108" s="58" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="109" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L109" s="57" t="s">
+      <c r="L109" t="s">
         <v>47</v>
       </c>
-      <c r="M109" s="57">
+      <c r="M109">
         <v>0.18879567553626506</v>
       </c>
-      <c r="N109" s="57">
+      <c r="N109">
         <v>2.1929402536023369E-2</v>
       </c>
-      <c r="O109" s="57">
+      <c r="O109">
         <v>8.6092484839078907</v>
       </c>
-      <c r="P109" s="57">
+      <c r="P109">
         <v>7.3616144627763752E-2</v>
       </c>
-      <c r="Q109" s="57">
+      <c r="Q109">
         <v>-8.9843802828436709E-2</v>
       </c>
-      <c r="R109" s="57">
+      <c r="R109">
         <v>0.46743515390096679</v>
       </c>
-      <c r="S109" s="57">
+      <c r="S109">
         <v>-8.9843802828436709E-2</v>
       </c>
-      <c r="T109" s="57">
+      <c r="T109">
         <v>0.46743515390096679</v>
       </c>
-      <c r="V109" s="57" t="s">
+      <c r="V109" t="s">
         <v>47</v>
       </c>
-      <c r="W109" s="57"/>
-      <c r="X109" s="57">
+      <c r="X109">
         <v>-9.3769809026318596E-2</v>
       </c>
-      <c r="Y109" s="57">
+      <c r="Y109">
         <v>7.6930167231322316E-2</v>
       </c>
-      <c r="Z109" s="57">
+      <c r="Z109">
         <v>-1.2188951668902648</v>
       </c>
-      <c r="AA109" s="57">
+      <c r="AA109">
         <v>0.43739967657341211</v>
       </c>
-      <c r="AB109" s="57">
+      <c r="AB109">
         <v>-1.0712602642556583</v>
       </c>
-      <c r="AC109" s="57">
+      <c r="AC109">
         <v>0.88372064620302127</v>
       </c>
-      <c r="AD109" s="57">
+      <c r="AD109">
         <v>-1.0712602642556583</v>
       </c>
-      <c r="AE109" s="57">
+      <c r="AE109">
         <v>0.88372064620302127</v>
       </c>
-      <c r="AG109" s="57" t="s">
+      <c r="AG109" t="s">
         <v>47</v>
       </c>
-      <c r="AH109" s="57">
+      <c r="AH109">
         <v>0.1383548060277589</v>
       </c>
-      <c r="AI109" s="57">
+      <c r="AI109">
         <v>9.7656701830491025E-3</v>
       </c>
-      <c r="AJ109" s="57">
+      <c r="AJ109">
         <v>14.167466587998248</v>
       </c>
-      <c r="AK109" s="57">
+      <c r="AK109">
         <v>4.4860926648346434E-2</v>
       </c>
-      <c r="AL109" s="57">
+      <c r="AL109">
         <v>1.4270201295980278E-2</v>
       </c>
-      <c r="AM109" s="57">
+      <c r="AM109">
         <v>0.26243941075953753</v>
       </c>
-      <c r="AN109" s="57">
+      <c r="AN109">
         <v>1.4270201295980278E-2</v>
       </c>
-      <c r="AO109" s="57">
+      <c r="AO109">
         <v>0.26243941075953753</v>
       </c>
-      <c r="AQ109" s="57" t="s">
+      <c r="AQ109" t="s">
         <v>47</v>
       </c>
-      <c r="AR109" s="57">
+      <c r="AR109">
         <v>-0.39159089074366649</v>
       </c>
-      <c r="AS109" s="57">
+      <c r="AS109">
         <v>0.1583535751041254</v>
       </c>
-      <c r="AT109" s="57">
+      <c r="AT109">
         <v>-2.4728894847254055</v>
       </c>
-      <c r="AU109" s="57">
+      <c r="AU109">
         <v>0.2446409005181292</v>
       </c>
-      <c r="AV109" s="57">
+      <c r="AV109">
         <v>-2.4036638367219014</v>
       </c>
-      <c r="AW109" s="57">
+      <c r="AW109">
         <v>1.6204820552345687</v>
       </c>
-      <c r="AX109" s="57">
+      <c r="AX109">
         <v>-2.4036638367219014</v>
       </c>
-      <c r="AY109" s="57">
+      <c r="AY109">
         <v>1.6204820552345687</v>
       </c>
     </row>
     <row r="110" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L110" s="58" t="s">
+      <c r="L110" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="M110" s="58">
+      <c r="M110" s="57">
         <v>2.7067637534479213E-2</v>
       </c>
-      <c r="N110" s="58">
+      <c r="N110" s="57">
         <v>1.1652603190141808E-2</v>
       </c>
-      <c r="O110" s="58">
+      <c r="O110" s="57">
         <v>2.3228833156679225</v>
       </c>
-      <c r="P110" s="58">
+      <c r="P110" s="57">
         <v>0.25879835026214726</v>
       </c>
-      <c r="Q110" s="58">
+      <c r="Q110" s="57">
         <v>-0.12099272430886512</v>
       </c>
-      <c r="R110" s="58">
+      <c r="R110" s="57">
         <v>0.17512799937782356</v>
       </c>
-      <c r="S110" s="58">
+      <c r="S110" s="57">
         <v>-0.12099272430886512</v>
       </c>
-      <c r="T110" s="58">
+      <c r="T110" s="57">
         <v>0.17512799937782356</v>
       </c>
-      <c r="V110" s="58" t="s">
+      <c r="V110" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="W110" s="58"/>
-      <c r="X110" s="58">
+      <c r="W110" s="57"/>
+      <c r="X110" s="57">
         <v>0.13961124664479449</v>
       </c>
-      <c r="Y110" s="58">
+      <c r="Y110" s="57">
         <v>4.0878300748288743E-2</v>
       </c>
-      <c r="Z110" s="58">
+      <c r="Z110" s="57">
         <v>3.4152898748032947</v>
       </c>
-      <c r="AA110" s="58">
+      <c r="AA110" s="57">
         <v>0.18133421153090104</v>
       </c>
-      <c r="AB110" s="58">
+      <c r="AB110" s="57">
         <v>-0.37979681192988601</v>
       </c>
-      <c r="AC110" s="58">
+      <c r="AC110" s="57">
         <v>0.65901930521947505</v>
       </c>
-      <c r="AD110" s="58">
+      <c r="AD110" s="57">
         <v>-0.37979681192988601</v>
       </c>
-      <c r="AE110" s="58">
+      <c r="AE110" s="57">
         <v>0.65901930521947505</v>
       </c>
-      <c r="AG110" s="58" t="s">
+      <c r="AG110" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AH110" s="58">
+      <c r="AH110" s="57">
         <v>1.4855246753621005E-2</v>
       </c>
-      <c r="AI110" s="58">
+      <c r="AI110" s="57">
         <v>5.1891737288300103E-3</v>
       </c>
-      <c r="AJ110" s="58">
+      <c r="AJ110" s="57">
         <v>2.8627383722167998</v>
       </c>
-      <c r="AK110" s="58">
+      <c r="AK110" s="57">
         <v>0.21394577442032442</v>
       </c>
-      <c r="AL110" s="58">
+      <c r="AL110" s="57">
         <v>-5.1079457056472238E-2</v>
       </c>
-      <c r="AM110" s="58">
+      <c r="AM110" s="57">
         <v>8.0789950563714241E-2</v>
       </c>
-      <c r="AN110" s="58">
+      <c r="AN110" s="57">
         <v>-5.1079457056472238E-2</v>
       </c>
-      <c r="AO110" s="58">
+      <c r="AO110" s="57">
         <v>8.0789950563714241E-2</v>
       </c>
-      <c r="AQ110" s="58" t="s">
+      <c r="AQ110" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AR110" s="58">
+      <c r="AR110" s="57">
         <v>3.3210709810304891E-2</v>
       </c>
-      <c r="AS110" s="58">
+      <c r="AS110" s="57">
         <v>8.4144169974422936E-2</v>
       </c>
-      <c r="AT110" s="58">
+      <c r="AT110" s="57">
         <v>0.39468818600741862</v>
       </c>
-      <c r="AU110" s="58">
+      <c r="AU110" s="57">
         <v>0.76068262316919966</v>
       </c>
-      <c r="AV110" s="58">
+      <c r="AV110" s="57">
         <v>-1.0359423412401974</v>
       </c>
-      <c r="AW110" s="58">
+      <c r="AW110" s="57">
         <v>1.1023637608608072</v>
       </c>
-      <c r="AX110" s="58">
+      <c r="AX110" s="57">
         <v>-1.0359423412401974</v>
       </c>
-      <c r="AY110" s="58">
+      <c r="AY110" s="57">
         <v>1.1023637608608072</v>
       </c>
     </row>
@@ -58523,156 +60478,152 @@
       </c>
     </row>
     <row r="113" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L113" s="60" t="s">
+      <c r="L113" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="M113" s="60"/>
-      <c r="V113" s="60" t="s">
+      <c r="M113" s="59"/>
+      <c r="V113" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="W113" s="60"/>
-      <c r="X113" s="60"/>
-      <c r="AG113" s="60" t="s">
+      <c r="W113" s="59"/>
+      <c r="X113" s="59"/>
+      <c r="AG113" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AH113" s="60"/>
-      <c r="AQ113" s="60" t="s">
+      <c r="AH113" s="59"/>
+      <c r="AQ113" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="AR113" s="60"/>
+      <c r="AR113" s="59"/>
     </row>
     <row r="114" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L114" s="57" t="s">
+      <c r="L114" t="s">
         <v>38</v>
       </c>
-      <c r="M114" s="57">
+      <c r="M114">
         <v>0.3606107512237875</v>
       </c>
-      <c r="V114" s="57" t="s">
+      <c r="V114" t="s">
         <v>38</v>
       </c>
-      <c r="W114" s="57"/>
-      <c r="X114" s="57">
+      <c r="X114">
         <v>0.22732386197621898</v>
       </c>
-      <c r="AG114" s="57" t="s">
+      <c r="AG114" t="s">
         <v>38</v>
       </c>
-      <c r="AH114" s="57">
+      <c r="AH114">
         <v>0.1931684215129188</v>
       </c>
-      <c r="AQ114" s="57" t="s">
+      <c r="AQ114" t="s">
         <v>38</v>
       </c>
-      <c r="AR114" s="57">
+      <c r="AR114">
         <v>0.33636457193983182</v>
       </c>
     </row>
     <row r="115" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L115" s="57" t="s">
+      <c r="L115" t="s">
         <v>39</v>
       </c>
-      <c r="M115" s="57">
+      <c r="M115">
         <v>0.13004011389818435</v>
       </c>
-      <c r="V115" s="57" t="s">
+      <c r="V115" t="s">
         <v>39</v>
       </c>
-      <c r="W115" s="57"/>
-      <c r="X115" s="57">
+      <c r="X115">
         <v>5.1676138223783058E-2</v>
       </c>
-      <c r="AG115" s="57" t="s">
+      <c r="AG115" t="s">
         <v>39</v>
       </c>
-      <c r="AH115" s="57">
+      <c r="AH115">
         <v>3.7314039069792665E-2</v>
       </c>
-      <c r="AQ115" s="57" t="s">
+      <c r="AQ115" t="s">
         <v>39</v>
       </c>
-      <c r="AR115" s="57">
+      <c r="AR115">
         <v>0.11314112525626628</v>
       </c>
     </row>
     <row r="116" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L116" s="57" t="s">
+      <c r="L116" t="s">
         <v>40</v>
       </c>
-      <c r="M116" s="57">
+      <c r="M116">
         <v>-4.3951863322178798E-2</v>
       </c>
-      <c r="V116" s="57" t="s">
+      <c r="V116" t="s">
         <v>40</v>
       </c>
-      <c r="W116" s="57"/>
-      <c r="X116" s="57">
+      <c r="X116">
         <v>-0.13798863413146031</v>
       </c>
-      <c r="AG116" s="57" t="s">
+      <c r="AG116" t="s">
         <v>40</v>
       </c>
-      <c r="AH116" s="57">
+      <c r="AH116">
         <v>-0.15522315311624882</v>
       </c>
-      <c r="AQ116" s="57" t="s">
+      <c r="AQ116" t="s">
         <v>40</v>
       </c>
-      <c r="AR116" s="57">
+      <c r="AR116">
         <v>-6.4230649692480463E-2</v>
       </c>
     </row>
     <row r="117" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L117" s="57" t="s">
+      <c r="L117" t="s">
         <v>41</v>
       </c>
-      <c r="M117" s="57">
+      <c r="M117">
         <v>5.1047612014651828E-2</v>
       </c>
-      <c r="V117" s="57" t="s">
+      <c r="V117" t="s">
         <v>41</v>
       </c>
-      <c r="W117" s="57"/>
-      <c r="X117" s="57">
+      <c r="X117">
         <v>3.2386367204997463E-2</v>
       </c>
-      <c r="AG117" s="57" t="s">
+      <c r="AG117" t="s">
         <v>41</v>
       </c>
-      <c r="AH117" s="57">
+      <c r="AH117">
         <v>3.6583708523595E-2</v>
       </c>
-      <c r="AQ117" s="57" t="s">
+      <c r="AQ117" t="s">
         <v>41</v>
       </c>
-      <c r="AR117" s="57">
+      <c r="AR117">
         <v>3.0016212161647234E-2</v>
       </c>
     </row>
     <row r="118" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L118" s="58" t="s">
+      <c r="L118" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="M118" s="58">
+      <c r="M118" s="57">
         <v>7</v>
       </c>
-      <c r="V118" s="58" t="s">
+      <c r="V118" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="W118" s="58"/>
-      <c r="X118" s="58">
+      <c r="W118" s="57"/>
+      <c r="X118" s="57">
         <v>7</v>
       </c>
-      <c r="AG118" s="58" t="s">
+      <c r="AG118" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AH118" s="58">
+      <c r="AH118" s="57">
         <v>7</v>
       </c>
-      <c r="AQ118" s="58" t="s">
+      <c r="AQ118" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="AR118" s="58">
+      <c r="AR118" s="57">
         <v>7</v>
       </c>
     </row>
@@ -58691,581 +60642,773 @@
       </c>
     </row>
     <row r="121" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L121" s="59"/>
-      <c r="M121" s="59" t="s">
+      <c r="L121" s="58"/>
+      <c r="M121" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="N121" s="59" t="s">
+      <c r="N121" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="O121" s="59" t="s">
+      <c r="O121" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="P121" s="59" t="s">
+      <c r="P121" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="Q121" s="59" t="s">
+      <c r="Q121" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="V121" s="59"/>
-      <c r="W121" s="59"/>
-      <c r="X121" s="59" t="s">
+      <c r="V121" s="58"/>
+      <c r="W121" s="58"/>
+      <c r="X121" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="Y121" s="59" t="s">
+      <c r="Y121" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="Z121" s="59" t="s">
+      <c r="Z121" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AA121" s="59" t="s">
+      <c r="AA121" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AB121" s="59" t="s">
+      <c r="AB121" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AG121" s="59"/>
-      <c r="AH121" s="59" t="s">
+      <c r="AG121" s="58"/>
+      <c r="AH121" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AI121" s="59" t="s">
+      <c r="AI121" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AJ121" s="59" t="s">
+      <c r="AJ121" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AK121" s="59" t="s">
+      <c r="AK121" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AL121" s="59" t="s">
+      <c r="AL121" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="AQ121" s="59"/>
-      <c r="AR121" s="59" t="s">
+      <c r="AQ121" s="58"/>
+      <c r="AR121" s="58" t="s">
         <v>48</v>
       </c>
-      <c r="AS121" s="59" t="s">
+      <c r="AS121" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="AT121" s="59" t="s">
+      <c r="AT121" s="58" t="s">
         <v>49</v>
       </c>
-      <c r="AU121" s="59" t="s">
+      <c r="AU121" s="58" t="s">
         <v>50</v>
       </c>
-      <c r="AV121" s="59" t="s">
+      <c r="AV121" s="58" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="122" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L122" s="57" t="s">
+      <c r="L122" t="s">
         <v>44</v>
       </c>
-      <c r="M122" s="57">
+      <c r="M122">
         <v>1</v>
       </c>
-      <c r="N122" s="57">
+      <c r="N122">
         <v>1.947596472984996E-3</v>
       </c>
-      <c r="O122" s="57">
+      <c r="O122">
         <v>1.947596472984996E-3</v>
       </c>
-      <c r="P122" s="57">
+      <c r="P122">
         <v>0.74739143709762446</v>
       </c>
-      <c r="Q122" s="57">
+      <c r="Q122">
         <v>0.42682398854131004</v>
       </c>
-      <c r="V122" s="57" t="s">
+      <c r="V122" t="s">
         <v>44</v>
       </c>
-      <c r="W122" s="57"/>
-      <c r="X122" s="57">
+      <c r="X122">
         <v>1</v>
       </c>
-      <c r="Y122" s="57">
+      <c r="Y122">
         <v>2.857773788353165E-4</v>
       </c>
-      <c r="Z122" s="57">
+      <c r="Z122">
         <v>2.857773788353165E-4</v>
       </c>
-      <c r="AA122" s="57">
+      <c r="AA122">
         <v>0.27246039199621797</v>
       </c>
-      <c r="AB122" s="57">
+      <c r="AB122">
         <v>0.62397660046449377</v>
       </c>
-      <c r="AG122" s="57" t="s">
+      <c r="AG122" t="s">
         <v>44</v>
       </c>
-      <c r="AH122" s="57">
+      <c r="AH122">
         <v>1</v>
       </c>
-      <c r="AI122" s="57">
+      <c r="AI122">
         <v>2.5937796835669765E-4</v>
       </c>
-      <c r="AJ122" s="57">
+      <c r="AJ122">
         <v>2.5937796835669765E-4</v>
       </c>
-      <c r="AK122" s="57">
+      <c r="AK122">
         <v>0.19380172031249687</v>
       </c>
-      <c r="AL122" s="57">
+      <c r="AL122">
         <v>0.67815095475821208</v>
       </c>
-      <c r="AQ122" s="57" t="s">
+      <c r="AQ122" t="s">
         <v>44</v>
       </c>
-      <c r="AR122" s="57">
+      <c r="AR122">
         <v>1</v>
       </c>
-      <c r="AS122" s="57">
+      <c r="AS122">
         <v>5.7470867746656478E-4</v>
       </c>
-      <c r="AT122" s="57">
+      <c r="AT122">
         <v>5.7470867746656478E-4</v>
       </c>
-      <c r="AU122" s="57">
+      <c r="AU122">
         <v>0.63787558809150713</v>
       </c>
-      <c r="AV122" s="57">
+      <c r="AV122">
         <v>0.46071740095907732</v>
       </c>
     </row>
     <row r="123" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L123" s="57" t="s">
+      <c r="L123" t="s">
         <v>45</v>
       </c>
-      <c r="M123" s="57">
+      <c r="M123">
         <v>5</v>
       </c>
-      <c r="N123" s="57">
+      <c r="N123">
         <v>1.3029293461992129E-2</v>
       </c>
-      <c r="O123" s="57">
+      <c r="O123">
         <v>2.6058586923984259E-3</v>
       </c>
-      <c r="P123" s="57"/>
-      <c r="Q123" s="57"/>
-      <c r="V123" s="57" t="s">
+      <c r="V123" t="s">
         <v>45</v>
       </c>
-      <c r="W123" s="57"/>
-      <c r="X123" s="57">
+      <c r="X123">
         <v>5</v>
       </c>
-      <c r="Y123" s="57">
+      <c r="Y123">
         <v>5.2443839036846757E-3</v>
       </c>
-      <c r="Z123" s="57">
+      <c r="Z123">
         <v>1.0488767807369352E-3</v>
       </c>
-      <c r="AA123" s="57"/>
-      <c r="AB123" s="57"/>
-      <c r="AG123" s="57" t="s">
+      <c r="AG123" t="s">
         <v>45</v>
       </c>
-      <c r="AH123" s="57">
+      <c r="AH123">
         <v>5</v>
       </c>
-      <c r="AI123" s="57">
+      <c r="AI123">
         <v>6.6918386466967867E-3</v>
       </c>
-      <c r="AJ123" s="57">
+      <c r="AJ123">
         <v>1.3383677293393574E-3</v>
       </c>
-      <c r="AK123" s="57"/>
-      <c r="AL123" s="57"/>
-      <c r="AQ123" s="57" t="s">
+      <c r="AQ123" t="s">
         <v>45</v>
       </c>
-      <c r="AR123" s="57">
+      <c r="AR123">
         <v>5</v>
       </c>
-      <c r="AS123" s="57">
+      <c r="AS123">
         <v>4.5048649626650969E-3</v>
       </c>
-      <c r="AT123" s="57">
+      <c r="AT123">
         <v>9.0097299253301942E-4</v>
       </c>
-      <c r="AU123" s="57"/>
-      <c r="AV123" s="57"/>
     </row>
     <row r="124" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L124" s="58" t="s">
+      <c r="L124" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="M124" s="58">
+      <c r="M124" s="57">
         <v>6</v>
       </c>
-      <c r="N124" s="58">
+      <c r="N124" s="57">
         <v>1.4976889934977125E-2</v>
       </c>
-      <c r="O124" s="58"/>
-      <c r="P124" s="58"/>
-      <c r="Q124" s="58"/>
-      <c r="V124" s="58" t="s">
+      <c r="O124" s="57"/>
+      <c r="P124" s="57"/>
+      <c r="Q124" s="57"/>
+      <c r="V124" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="W124" s="58"/>
-      <c r="X124" s="58">
+      <c r="W124" s="57"/>
+      <c r="X124" s="57">
         <v>6</v>
       </c>
-      <c r="Y124" s="58">
+      <c r="Y124" s="57">
         <v>5.5301612825199922E-3</v>
       </c>
-      <c r="Z124" s="58"/>
-      <c r="AA124" s="58"/>
-      <c r="AB124" s="58"/>
-      <c r="AG124" s="58" t="s">
+      <c r="Z124" s="57"/>
+      <c r="AA124" s="57"/>
+      <c r="AB124" s="57"/>
+      <c r="AG124" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AH124" s="58">
+      <c r="AH124" s="57">
         <v>6</v>
       </c>
-      <c r="AI124" s="58">
+      <c r="AI124" s="57">
         <v>6.9512166150534844E-3</v>
       </c>
-      <c r="AJ124" s="58"/>
-      <c r="AK124" s="58"/>
-      <c r="AL124" s="58"/>
-      <c r="AQ124" s="58" t="s">
+      <c r="AJ124" s="57"/>
+      <c r="AK124" s="57"/>
+      <c r="AL124" s="57"/>
+      <c r="AQ124" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="AR124" s="58">
+      <c r="AR124" s="57">
         <v>6</v>
       </c>
-      <c r="AS124" s="58">
+      <c r="AS124" s="57">
         <v>5.0795736401316616E-3</v>
       </c>
-      <c r="AT124" s="58"/>
-      <c r="AU124" s="58"/>
-      <c r="AV124" s="58"/>
+      <c r="AT124" s="57"/>
+      <c r="AU124" s="57"/>
+      <c r="AV124" s="57"/>
     </row>
     <row r="125" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="126" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L126" s="59"/>
-      <c r="M126" s="59" t="s">
+      <c r="L126" s="58"/>
+      <c r="M126" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="N126" s="59" t="s">
+      <c r="N126" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="O126" s="59" t="s">
+      <c r="O126" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="P126" s="59" t="s">
+      <c r="P126" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="Q126" s="59" t="s">
+      <c r="Q126" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="R126" s="59" t="s">
+      <c r="R126" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="S126" s="59" t="s">
+      <c r="S126" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="T126" s="59" t="s">
+      <c r="T126" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="V126" s="59"/>
-      <c r="W126" s="59"/>
-      <c r="X126" s="59" t="s">
+      <c r="V126" s="58"/>
+      <c r="W126" s="58"/>
+      <c r="X126" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="Y126" s="59" t="s">
+      <c r="Y126" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="Z126" s="59" t="s">
+      <c r="Z126" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AA126" s="59" t="s">
+      <c r="AA126" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AB126" s="59" t="s">
+      <c r="AB126" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AC126" s="59" t="s">
+      <c r="AC126" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AD126" s="59" t="s">
+      <c r="AD126" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AE126" s="59" t="s">
+      <c r="AE126" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AG126" s="59"/>
-      <c r="AH126" s="59" t="s">
+      <c r="AG126" s="58"/>
+      <c r="AH126" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AI126" s="59" t="s">
+      <c r="AI126" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AJ126" s="59" t="s">
+      <c r="AJ126" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AK126" s="59" t="s">
+      <c r="AK126" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AL126" s="59" t="s">
+      <c r="AL126" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AM126" s="59" t="s">
+      <c r="AM126" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AN126" s="59" t="s">
+      <c r="AN126" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AO126" s="59" t="s">
+      <c r="AO126" s="58" t="s">
         <v>58</v>
       </c>
-      <c r="AQ126" s="59"/>
-      <c r="AR126" s="59" t="s">
+      <c r="AQ126" s="58"/>
+      <c r="AR126" s="58" t="s">
         <v>52</v>
       </c>
-      <c r="AS126" s="59" t="s">
+      <c r="AS126" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="AT126" s="59" t="s">
+      <c r="AT126" s="58" t="s">
         <v>53</v>
       </c>
-      <c r="AU126" s="59" t="s">
+      <c r="AU126" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="AV126" s="59" t="s">
+      <c r="AV126" s="58" t="s">
         <v>55</v>
       </c>
-      <c r="AW126" s="59" t="s">
+      <c r="AW126" s="58" t="s">
         <v>56</v>
       </c>
-      <c r="AX126" s="59" t="s">
+      <c r="AX126" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="AY126" s="59" t="s">
+      <c r="AY126" s="58" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="127" spans="12:51" x14ac:dyDescent="0.25">
-      <c r="L127" s="57" t="s">
+      <c r="L127" t="s">
         <v>47</v>
       </c>
-      <c r="M127" s="57">
+      <c r="M127">
         <v>5.1314348645439316E-2</v>
       </c>
-      <c r="N127" s="57">
+      <c r="N127">
         <v>2.9184555250735465E-2</v>
       </c>
-      <c r="O127" s="57">
+      <c r="O127">
         <v>1.758270708756001</v>
       </c>
-      <c r="P127" s="57">
+      <c r="P127">
         <v>0.13903275884487903</v>
       </c>
-      <c r="Q127" s="57">
+      <c r="Q127">
         <v>-2.3706938963225711E-2</v>
       </c>
-      <c r="R127" s="57">
+      <c r="R127">
         <v>0.12633563625410435</v>
       </c>
-      <c r="S127" s="57">
+      <c r="S127">
         <v>-2.3706938963225711E-2</v>
       </c>
-      <c r="T127" s="57">
+      <c r="T127">
         <v>0.12633563625410435</v>
       </c>
-      <c r="V127" s="57" t="s">
+      <c r="V127" t="s">
         <v>47</v>
       </c>
-      <c r="W127" s="57"/>
-      <c r="X127" s="57">
+      <c r="X127">
         <v>1.3353129222556138E-2</v>
       </c>
-      <c r="Y127" s="57">
+      <c r="Y127">
         <v>1.8515689290099738E-2</v>
       </c>
-      <c r="Z127" s="57">
+      <c r="Z127">
         <v>0.72117915856883608</v>
       </c>
-      <c r="AA127" s="57">
+      <c r="AA127">
         <v>0.50310072459638144</v>
       </c>
-      <c r="AB127" s="57">
+      <c r="AB127">
         <v>-3.4242965340860104E-2</v>
       </c>
-      <c r="AC127" s="57">
+      <c r="AC127">
         <v>6.0949223785972381E-2</v>
       </c>
-      <c r="AD127" s="57">
+      <c r="AD127">
         <v>-3.4242965340860104E-2</v>
       </c>
-      <c r="AE127" s="57">
+      <c r="AE127">
         <v>6.0949223785972381E-2</v>
       </c>
-      <c r="AG127" s="57" t="s">
+      <c r="AG127" t="s">
         <v>47</v>
       </c>
-      <c r="AH127" s="57">
+      <c r="AH127">
         <v>0.10530570105480742</v>
       </c>
-      <c r="AI127" s="57">
+      <c r="AI127">
         <v>2.0915361572196794E-2</v>
       </c>
-      <c r="AJ127" s="57">
+      <c r="AJ127">
         <v>5.0348496578128676</v>
       </c>
-      <c r="AK127" s="57">
+      <c r="AK127">
         <v>3.9843303382965708E-3</v>
       </c>
-      <c r="AL127" s="57">
+      <c r="AL127">
         <v>5.1541052511552547E-2</v>
       </c>
-      <c r="AM127" s="57">
+      <c r="AM127">
         <v>0.15907034959806229</v>
       </c>
-      <c r="AN127" s="57">
+      <c r="AN127">
         <v>5.1541052511552547E-2</v>
       </c>
-      <c r="AO127" s="57">
+      <c r="AO127">
         <v>0.15907034959806229</v>
       </c>
-      <c r="AQ127" s="57" t="s">
+      <c r="AQ127" t="s">
         <v>47</v>
       </c>
-      <c r="AR127" s="57">
+      <c r="AR127">
         <v>6.1054860940162681E-3</v>
       </c>
-      <c r="AS127" s="57">
+      <c r="AS127">
         <v>1.716064214713818E-2</v>
       </c>
-      <c r="AT127" s="57">
+      <c r="AT127">
         <v>0.35578424406655773</v>
       </c>
-      <c r="AU127" s="57">
+      <c r="AU127">
         <v>0.73652056618626793</v>
       </c>
-      <c r="AV127" s="57">
+      <c r="AV127">
         <v>-3.8007348897272114E-2</v>
       </c>
-      <c r="AW127" s="57">
+      <c r="AW127">
         <v>5.0218321085304649E-2</v>
       </c>
-      <c r="AX127" s="57">
+      <c r="AX127">
         <v>-3.8007348897272114E-2</v>
       </c>
-      <c r="AY127" s="57">
+      <c r="AY127">
         <v>5.0218321085304649E-2</v>
       </c>
     </row>
     <row r="128" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="L128" s="58" t="s">
+      <c r="L128" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="M128" s="58">
+      <c r="M128" s="57">
         <v>9.8156776994206864E-3</v>
       </c>
-      <c r="N128" s="58">
+      <c r="N128" s="57">
         <v>1.1353930483895772E-2</v>
       </c>
-      <c r="O128" s="58">
+      <c r="O128" s="57">
         <v>0.86451803746227629</v>
       </c>
-      <c r="P128" s="58">
+      <c r="P128" s="57">
         <v>0.42682398854130932</v>
       </c>
-      <c r="Q128" s="58">
+      <c r="Q128" s="57">
         <v>-1.9370529765559221E-2</v>
       </c>
-      <c r="R128" s="58">
+      <c r="R128" s="57">
         <v>3.900188516440059E-2</v>
       </c>
-      <c r="S128" s="58">
+      <c r="S128" s="57">
         <v>-1.9370529765559221E-2</v>
       </c>
-      <c r="T128" s="58">
+      <c r="T128" s="57">
         <v>3.900188516440059E-2</v>
       </c>
-      <c r="V128" s="58" t="s">
+      <c r="V128" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="W128" s="58"/>
-      <c r="X128" s="58">
+      <c r="W128" s="57"/>
+      <c r="X128" s="57">
         <v>3.7599729829936967E-3</v>
       </c>
-      <c r="Y128" s="58">
+      <c r="Y128" s="57">
         <v>7.2033254320676377E-3</v>
       </c>
-      <c r="Z128" s="58">
+      <c r="Z128" s="57">
         <v>0.52197738647973824</v>
       </c>
-      <c r="AA128" s="58">
+      <c r="AA128" s="57">
         <v>0.62397660046449377</v>
       </c>
-      <c r="AB128" s="58">
+      <c r="AB128" s="57">
         <v>-1.4756764528856482E-2</v>
       </c>
-      <c r="AC128" s="58">
+      <c r="AC128" s="57">
         <v>2.2276710494843876E-2</v>
       </c>
-      <c r="AD128" s="58">
+      <c r="AD128" s="57">
         <v>-1.4756764528856482E-2</v>
       </c>
-      <c r="AE128" s="58">
+      <c r="AE128" s="57">
         <v>2.2276710494843876E-2</v>
       </c>
-      <c r="AG128" s="58" t="s">
+      <c r="AG128" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AH128" s="58">
+      <c r="AH128" s="57">
         <v>3.5820970016607109E-3</v>
       </c>
-      <c r="AI128" s="58">
+      <c r="AI128" s="57">
         <v>8.1368915611719998E-3</v>
       </c>
-      <c r="AJ128" s="58">
+      <c r="AJ128" s="57">
         <v>0.44022916794835132</v>
       </c>
-      <c r="AK128" s="58">
+      <c r="AK128" s="57">
         <v>0.67815095475821141</v>
       </c>
-      <c r="AL128" s="58">
+      <c r="AL128" s="57">
         <v>-1.7334448644030449E-2</v>
       </c>
-      <c r="AM128" s="58">
+      <c r="AM128" s="57">
         <v>2.4498642647351875E-2</v>
       </c>
-      <c r="AN128" s="58">
+      <c r="AN128" s="57">
         <v>-1.7334448644030449E-2</v>
       </c>
-      <c r="AO128" s="58">
+      <c r="AO128" s="57">
         <v>2.4498642647351875E-2</v>
       </c>
-      <c r="AQ128" s="58" t="s">
+      <c r="AQ128" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="AR128" s="58">
+      <c r="AR128" s="57">
         <v>5.332055697997151E-3</v>
       </c>
-      <c r="AS128" s="58">
+      <c r="AS128" s="57">
         <v>6.6761592329802151E-3</v>
       </c>
-      <c r="AT128" s="58">
+      <c r="AT128" s="57">
         <v>0.79867113888728192</v>
       </c>
-      <c r="AU128" s="58">
+      <c r="AU128" s="57">
         <v>0.46071740095907665</v>
       </c>
-      <c r="AV128" s="58">
+      <c r="AV128" s="57">
         <v>-1.1829557958117461E-2</v>
       </c>
-      <c r="AW128" s="58">
+      <c r="AW128" s="57">
         <v>2.2493669354111765E-2</v>
       </c>
-      <c r="AX128" s="58">
+      <c r="AX128" s="57">
         <v>-1.1829557958117461E-2</v>
       </c>
-      <c r="AY128" s="58">
+      <c r="AY128" s="57">
         <v>2.2493669354111765E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{417B3731-F602-4487-9B88-A7F91293C15D}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0.78479742735639801</v>
+      </c>
+      <c r="C2" s="23">
+        <v>0.57681691180727601</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="16">
+        <v>0.17369777575697301</v>
+      </c>
+      <c r="C3" s="23">
+        <v>0.13233171245622599</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="16">
+        <v>9.9143945152060597E-2</v>
+      </c>
+      <c r="C4" s="23">
+        <v>8.9326261366187695E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="16">
+        <v>0.21234239309632399</v>
+      </c>
+      <c r="C5" s="23">
+        <v>0.14884070399999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="16">
+        <v>0.36516163611226798</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.164262280281398</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="55">
+        <v>4.1333778886518201E-2</v>
+      </c>
+      <c r="C7" s="22">
+        <v>-4.45444212598241E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="55">
+        <v>9.4513218106104094E-2</v>
+      </c>
+      <c r="C8" s="16">
+        <v>5.1856335362832198E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="55">
+        <v>4.2663094228711902E-2</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0.103368750113241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="55">
+        <v>8.8732929175135894E-2</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0.15621819275209001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="60">
+        <v>-1.9463558010346702E-2</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0.15071577677020101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="16">
+        <v>0.10415722716452799</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5.5397551503622099E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="16">
+        <v>4.66251429291673E-2</v>
+      </c>
+      <c r="C13" s="16">
+        <v>6.9883057908481996E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="16">
+        <v>9.0894558490112708E-3</v>
+      </c>
+      <c r="C14" s="16">
+        <v>7.8645648239850305E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="24">
+        <v>-1.7278096303121701E-2</v>
+      </c>
+      <c r="C15" s="16">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="16">
+        <v>2.0373962034653699E-2</v>
+      </c>
+      <c r="C16" s="16">
+        <v>0.101236914763633</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="24">
+        <v>-2.50118292734785E-2</v>
+      </c>
+      <c r="C17" s="16">
+        <v>0.107400232693555</v>
       </c>
     </row>
   </sheetData>

--- a/correlations/HI_tauc/HI_tauc_correlations_V2_predefense.xlsx
+++ b/correlations/HI_tauc/HI_tauc_correlations_V2_predefense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huck4481\Documents\GitHub\hysteresis\correlations\HI_tauc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529151E7-A44D-4E04-9DB0-4BD2B792916E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB479D18-7397-4AB7-9516-814B30B56F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="360" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{867610DC-2157-4A8B-BAD4-C3624B9432BC}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="87">
   <si>
     <t>Storm</t>
   </si>
@@ -291,6 +291,18 @@
   <si>
     <t>tauc relative to peak (hrs)</t>
   </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>Silt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fine Sand </t>
+  </si>
+  <si>
+    <t>∆transport</t>
+  </si>
 </sst>
 </file>
 
@@ -503,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -665,6 +677,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -24395,6 +24410,3261 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>Clay to </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>peak / </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>c50</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$C$95:$C$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.111966393265454</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5194138495455596E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13829255988935801</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$G$95:$G$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.1737788669959504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0182769682576838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-5571-45F0-A3EE-1C1EC068B967}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Silt to </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>peak / </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>c50</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$D$95:$D$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.120049397034174</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10817436709775199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.136626644156328</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$G$95:$G$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.1737788669959504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0182769682576838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4E68-42F8-BCBF-D8719E60D135}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart35.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Fine Sand to </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>peak / </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="el-GR">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>τ</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US">
+                <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>c50</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$E$95:$E$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.19303664781799701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.8535674621076102E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.135540384510944</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$G$95:$G$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.1737788669959504</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.0182769682576838</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-446E-4192-A2EA-49115014581C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart36.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Clay to ∆transport</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$C$95:$C$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.111966393265454</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5194138495455596E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13829255988935801</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$H$95:$H$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-69C0-4853-AF4C-614DA99CD11D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart37.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Silt to ∆transport</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$D$95:$D$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.120049397034174</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.10817436709775199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.136626644156328</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$H$95:$H$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-479E-4FCA-8835-92777AA69D6D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart38.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Fine Sand to ∆transport</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3212164765087942"/>
+          <c:y val="4.2457904826093087E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23386447129231622"/>
+          <c:y val="0.16881658193755791"/>
+          <c:w val="0.71225510689966409"/>
+          <c:h val="0.60779316659887139"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.34292271315313644"/>
+                  <c:y val="7.6931049031190843E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'no st7'!$E$95:$E$97</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.19303664781799701</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.8535674621076102E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.135540384510944</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'no st7'!$H$95:$H$97</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1656-48A7-A26C-5A19D552FEFE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="482930495"/>
+        <c:axId val="482950655"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="482930495"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Hysteresis Index</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.47359775592744585"/>
+              <c:y val="0.827214977788848"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482950655"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="482950655"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>τ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US">
+                    <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>c50</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="482930495"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart39.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Spring</a:t>
             </a:r>
           </a:p>
@@ -24727,404 +27997,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="1299336592"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart34.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Summer</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="38100" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="0"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="-0.12952209098862641"/>
-                  <c:y val="-3.7116870807815693E-2"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'turb vs SS HI'!$B$2:$B$7</c:f>
-              <c:numCache>
-                <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.78479742735639801</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.17369777575697301</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9.9143945152060597E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.21234239309632399</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.36516163611226798</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.1333778886518201E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'turb vs SS HI'!$C$2:$C$7</c:f>
-              <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>0.57681691180727601</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13233171245622599</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>8.9326261366187695E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14884070399999999</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.164262280281398</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-4.45444212598241E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B59C-477A-96C7-97827DE0BAEE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1351180048"/>
-        <c:axId val="1113714800"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1351180048"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1113714800"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1113714800"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1351180048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -26076,6 +28948,404 @@
         </a:p>
       </c:txPr>
     </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart40.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Summer</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.12952209098862641"/>
+                  <c:y val="-3.7116870807815693E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$B$2:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.78479742735639801</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.17369777575697301</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.9143945152060597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.21234239309632399</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.36516163611226798</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.1333778886518201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'turb vs SS HI'!$C$2:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.57681691180727601</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13233171245622599</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.9326261366187695E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.14884070399999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.164262280281398</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4.45444212598241E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B59C-477A-96C7-97827DE0BAEE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1351180048"/>
+        <c:axId val="1113714800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1351180048"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1113714800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1113714800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1351180048"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -31775,7 +35045,247 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors35.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors36.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors37.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors38.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors39.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors40.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -46463,7 +49973,3103 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style35.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style36.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style37.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style38.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style39.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style40.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -50592,16 +57198,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>463826</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>171011</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>574204</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>110499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>935935</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>56711</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>656909</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>186699</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -50775,6 +57381,234 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>560294</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>22412</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>321541</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>123265</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{285B209B-69A1-4A79-85A8-3B885D4161D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>33618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142248</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>134471</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Chart 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A52FA6D5-B479-4F0D-BBFA-726FB6F2502B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>224119</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>11205</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1173190</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>112058</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="17" name="Chart 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F94BFFB9-CB7A-4022-83BE-5440A663AD45}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>605118</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>366365</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>156882</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="22" name="Chart 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C96F5E7-9976-4404-94CD-BDD3F357BE64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId21"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>403412</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>164660</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="23" name="Chart 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D593A4F3-2E57-4DC8-B851-D3B108E8467F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>235323</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>156883</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1184394</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="24" name="Chart 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A32339-AE25-4246-979D-81BC431FF63B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId23"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -59600,8 +66434,10 @@
       </c>
     </row>
     <row r="92" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
+      <c r="A92" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B92" s="7"/>
       <c r="C92" s="8"/>
       <c r="L92" s="57" t="s">
         <v>67</v>
@@ -59713,15 +66549,51 @@
         <v>8.2913105163014728E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="8"/>
+    <row r="93" spans="1:51" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="F93" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H93" s="13" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="94" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="8"/>
+      <c r="A94" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B94" s="16">
+        <v>0.78479742735639801</v>
+      </c>
+      <c r="C94" s="6">
+        <v>0.82639610482808601</v>
+      </c>
+      <c r="D94" s="6">
+        <v>0.81089291747742998</v>
+      </c>
+      <c r="E94" s="6">
+        <v>0.68761829144305897</v>
+      </c>
+      <c r="F94" s="17"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="15"/>
       <c r="L94" t="s">
         <v>69</v>
       </c>
@@ -59733,6 +66605,30 @@
       </c>
     </row>
     <row r="95" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A95" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" s="16">
+        <v>0.17369777575697301</v>
+      </c>
+      <c r="C95" s="6">
+        <v>0.111966393265454</v>
+      </c>
+      <c r="D95" s="6">
+        <v>0.120049397034174</v>
+      </c>
+      <c r="E95" s="6">
+        <v>0.19303664781799701</v>
+      </c>
+      <c r="F95" s="18">
+        <v>60.588347259999999</v>
+      </c>
+      <c r="G95" s="18">
+        <v>1.1737788669959504</v>
+      </c>
+      <c r="H95" s="15">
+        <v>0.25</v>
+      </c>
       <c r="L95" s="59" t="s">
         <v>37</v>
       </c>
@@ -59752,6 +66648,30 @@
       <c r="AR95" s="59"/>
     </row>
     <row r="96" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A96" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" s="16">
+        <v>9.9143945152060597E-2</v>
+      </c>
+      <c r="C96" s="6">
+        <v>8.5194138495455596E-2</v>
+      </c>
+      <c r="D96" s="6">
+        <v>0.10817436709775199</v>
+      </c>
+      <c r="E96" s="6">
+        <v>8.8535674621076102E-2</v>
+      </c>
+      <c r="F96" s="18">
+        <v>73.387016439999996</v>
+      </c>
+      <c r="G96" s="18">
+        <v>1.0182769682576838</v>
+      </c>
+      <c r="H96" s="15">
+        <v>-3.25</v>
+      </c>
       <c r="L96" t="s">
         <v>38</v>
       </c>
@@ -59777,7 +66697,31 @@
         <v>0.36712737728751571</v>
       </c>
     </row>
-    <row r="97" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A97" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B97" s="16">
+        <v>0.21234239309632399</v>
+      </c>
+      <c r="C97" s="6">
+        <v>0.13829255988935801</v>
+      </c>
+      <c r="D97" s="6">
+        <v>0.136626644156328</v>
+      </c>
+      <c r="E97" s="6">
+        <v>0.135540384510944</v>
+      </c>
+      <c r="F97" s="18">
+        <v>79.767295559999994</v>
+      </c>
+      <c r="G97" s="18">
+        <v>1</v>
+      </c>
+      <c r="H97" s="15">
+        <v>0</v>
+      </c>
       <c r="L97" t="s">
         <v>39</v>
       </c>
@@ -59803,7 +66747,25 @@
         <v>0.13478251115400991</v>
       </c>
     </row>
-    <row r="98" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" s="16">
+        <v>0.36516163611226798</v>
+      </c>
+      <c r="C98" s="6">
+        <v>-0.114348261169542</v>
+      </c>
+      <c r="D98" s="6">
+        <v>-0.113414678070824</v>
+      </c>
+      <c r="E98" s="6">
+        <v>0.19158277625082301</v>
+      </c>
+      <c r="F98" s="18"/>
+      <c r="G98" s="18"/>
+      <c r="H98" s="15"/>
       <c r="L98" t="s">
         <v>40</v>
       </c>
@@ -59829,7 +66791,25 @@
         <v>-0.73043497769198018</v>
       </c>
     </row>
-    <row r="99" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A99" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B99" s="16">
+        <v>4.1333778886518201E-2</v>
+      </c>
+      <c r="C99" s="6">
+        <v>4.0979442194653999E-2</v>
+      </c>
+      <c r="D99" s="6">
+        <v>4.3152266392038501E-2</v>
+      </c>
+      <c r="E99" s="6">
+        <v>4.9298883225582402E-2</v>
+      </c>
+      <c r="F99" s="18"/>
+      <c r="G99" s="18"/>
+      <c r="H99" s="15"/>
       <c r="L99" t="s">
         <v>41</v>
       </c>
@@ -59855,7 +66835,25 @@
         <v>0.23235068371476744</v>
       </c>
     </row>
-    <row r="100" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B100" s="16">
+        <v>9.4513218106104094E-2</v>
+      </c>
+      <c r="C100" s="6">
+        <v>3.7096821663735999E-2</v>
+      </c>
+      <c r="D100" s="6">
+        <v>4.1729808309260499E-2</v>
+      </c>
+      <c r="E100" s="6">
+        <v>0.417116565148758</v>
+      </c>
+      <c r="F100" s="50"/>
+      <c r="G100" s="18"/>
+      <c r="H100" s="15"/>
       <c r="L100" s="57" t="s">
         <v>42</v>
       </c>
@@ -59882,7 +66880,42 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A101" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101" s="16">
+        <v>4.2663094228711902E-2</v>
+      </c>
+      <c r="C101" s="6">
+        <v>5.46373008647544E-2</v>
+      </c>
+      <c r="D101" s="6">
+        <v>8.4884621005949706E-2</v>
+      </c>
+      <c r="E101" s="6">
+        <v>9.0589300214318305E-4</v>
+      </c>
+      <c r="F101" s="50"/>
+      <c r="G101" s="18"/>
+      <c r="H101" s="15"/>
+    </row>
+    <row r="102" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" s="16">
+        <v>8.8732929175135894E-2</v>
+      </c>
+      <c r="F102" s="18">
+        <v>110.72040256</v>
+      </c>
+      <c r="G102" s="18">
+        <v>1.0393698938576728</v>
+      </c>
+      <c r="H102" s="15">
+        <v>-0.75</v>
+      </c>
       <c r="L102" t="s">
         <v>43</v>
       </c>
@@ -59896,7 +66929,16 @@
         <v>43</v>
       </c>
     </row>
-    <row r="103" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A103" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="24">
+        <v>-1.9463558010346702E-2</v>
+      </c>
+      <c r="F103" s="18"/>
+      <c r="G103" s="18"/>
+      <c r="H103" s="15"/>
       <c r="L103" s="58"/>
       <c r="M103" s="58" t="s">
         <v>48</v>
@@ -59963,7 +67005,22 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A104" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" s="16">
+        <v>0.10415722716452799</v>
+      </c>
+      <c r="F104" s="18">
+        <v>111.66319882000001</v>
+      </c>
+      <c r="G104" s="18">
+        <v>1.0331150820718804</v>
+      </c>
+      <c r="H104" s="15">
+        <v>-1</v>
+      </c>
       <c r="L104" t="s">
         <v>44</v>
       </c>
@@ -60037,7 +67094,22 @@
         <v>0.76068262316919988</v>
       </c>
     </row>
-    <row r="105" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A105" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B105" s="16">
+        <v>4.66251429291673E-2</v>
+      </c>
+      <c r="F105" s="18">
+        <v>114.89097618</v>
+      </c>
+      <c r="G105" s="18">
+        <v>1.0275460447393339</v>
+      </c>
+      <c r="H105" s="15">
+        <v>-1.25</v>
+      </c>
       <c r="L105" t="s">
         <v>45</v>
       </c>
@@ -60087,7 +67159,22 @@
         <v>5.3986840222719899E-2</v>
       </c>
     </row>
-    <row r="106" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B106" s="16">
+        <v>9.0894558490112708E-3</v>
+      </c>
+      <c r="F106" s="18">
+        <v>116.55531655999999</v>
+      </c>
+      <c r="G106" s="18">
+        <v>1.0275826446035865</v>
+      </c>
+      <c r="H106" s="15">
+        <v>-3.5</v>
+      </c>
       <c r="L106" s="57" t="s">
         <v>46</v>
       </c>
@@ -60138,8 +67225,39 @@
       <c r="AU106" s="57"/>
       <c r="AV106" s="57"/>
     </row>
-    <row r="107" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="108" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B107" s="24">
+        <v>-1.7278096303121701E-2</v>
+      </c>
+      <c r="F107" s="18">
+        <v>120.40602251999999</v>
+      </c>
+      <c r="G107" s="18">
+        <v>1.0396485920727681</v>
+      </c>
+      <c r="H107" s="15">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="108" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A108" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B108" s="16">
+        <v>2.0373962034653699E-2</v>
+      </c>
+      <c r="F108" s="18">
+        <v>118.75512236</v>
+      </c>
+      <c r="G108" s="18">
+        <v>1.0831630031367767</v>
+      </c>
+      <c r="H108" s="15">
+        <v>-3.5</v>
+      </c>
       <c r="L108" s="58"/>
       <c r="M108" s="58" t="s">
         <v>52</v>
@@ -60242,7 +67360,22 @@
         <v>58</v>
       </c>
     </row>
-    <row r="109" spans="12:51" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A109" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B109" s="24">
+        <v>-2.50118292734785E-2</v>
+      </c>
+      <c r="F109" s="18">
+        <v>125.12197168</v>
+      </c>
+      <c r="G109" s="18">
+        <v>1.0183454205725238</v>
+      </c>
+      <c r="H109" s="15">
+        <v>-4.25</v>
+      </c>
       <c r="L109" t="s">
         <v>47</v>
       </c>
@@ -60352,7 +67485,7 @@
         <v>1.6204820552345687</v>
       </c>
     </row>
-    <row r="110" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L110" s="57" t="s">
         <v>67</v>
       </c>
@@ -60463,7 +67596,7 @@
         <v>1.1023637608608072</v>
       </c>
     </row>
-    <row r="112" spans="12:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="L112" t="s">
         <v>70</v>
       </c>
